--- a/research/traditional_assets/database/data/chile/chile_shoe.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_shoe.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09342894615859433</v>
+        <v>0.09320953800396614</v>
       </c>
       <c r="C2">
-        <v>491.2275030333482</v>
+        <v>488.286560953619</v>
       </c>
       <c r="D2">
-        <v>466.5275030333482</v>
+        <v>468.6865609536191</v>
       </c>
       <c r="E2">
-        <v>-63.8</v>
+        <v>-58.7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.100000000000001</v>
       </c>
       <c r="G2">
         <v>24.7</v>
@@ -1451,28 +1451,28 @@
         <v>39.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.25653</v>
       </c>
       <c r="N2">
-        <v>39.6</v>
+        <v>39.34347</v>
       </c>
       <c r="O2">
-        <v>10.692</v>
+        <v>10.6227369</v>
       </c>
       <c r="P2">
-        <v>28.908</v>
+        <v>28.7207331</v>
       </c>
       <c r="Q2">
-        <v>36.608</v>
+        <v>36.4207331</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09342894615859433</v>
+        <v>0.09378014949895569</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896529</v>
+        <v>0.8787732880058898</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>154.3679101859431</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09320953800396614</v>
+        <v>0.09299012984933794</v>
       </c>
       <c r="C3">
-        <v>488.286560953619</v>
+        <v>485.365695738079</v>
       </c>
       <c r="D3">
-        <v>468.6865609536191</v>
+        <v>470.865695738079</v>
       </c>
       <c r="E3">
-        <v>-58.7</v>
+        <v>-53.59999999999999</v>
       </c>
       <c r="F3">
-        <v>5.100000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G3">
         <v>24.7</v>
@@ -1533,28 +1533,28 @@
         <v>39.6</v>
       </c>
       <c r="M3">
-        <v>0.25653</v>
+        <v>0.5130600000000001</v>
       </c>
       <c r="N3">
-        <v>39.34347</v>
+        <v>39.08694</v>
       </c>
       <c r="O3">
-        <v>10.6227369</v>
+        <v>10.5534738</v>
       </c>
       <c r="P3">
-        <v>28.7207331</v>
+        <v>28.5334662</v>
       </c>
       <c r="Q3">
-        <v>36.4207331</v>
+        <v>36.2334662</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09378014949895569</v>
+        <v>0.09413852025442646</v>
       </c>
       <c r="T3">
-        <v>0.8787732880058898</v>
+        <v>0.8853369742469478</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.3679101859431</v>
+        <v>77.18395509297157</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09299012984933794</v>
+        <v>0.09277072169470971</v>
       </c>
       <c r="C4">
-        <v>485.365695738079</v>
+        <v>482.4651887339736</v>
       </c>
       <c r="D4">
-        <v>470.865695738079</v>
+        <v>473.0651887339736</v>
       </c>
       <c r="E4">
-        <v>-53.59999999999999</v>
+        <v>-48.5</v>
       </c>
       <c r="F4">
-        <v>10.2</v>
+        <v>15.3</v>
       </c>
       <c r="G4">
         <v>24.7</v>
@@ -1615,28 +1615,28 @@
         <v>39.6</v>
       </c>
       <c r="M4">
-        <v>0.5130600000000001</v>
+        <v>0.7695899999999999</v>
       </c>
       <c r="N4">
-        <v>39.08694</v>
+        <v>38.83041</v>
       </c>
       <c r="O4">
-        <v>10.5534738</v>
+        <v>10.4842107</v>
       </c>
       <c r="P4">
-        <v>28.5334662</v>
+        <v>28.3461993</v>
       </c>
       <c r="Q4">
-        <v>36.2334662</v>
+        <v>36.0461993</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09413852025442646</v>
+        <v>0.09450428009763888</v>
       </c>
       <c r="T4">
-        <v>0.8853369742469478</v>
+        <v>0.8920359942249347</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.18395509297157</v>
+        <v>51.45597006198106</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09277072169470971</v>
+        <v>0.0925513135400815</v>
       </c>
       <c r="C5">
-        <v>482.4651887339736</v>
+        <v>479.5853265701005</v>
       </c>
       <c r="D5">
-        <v>473.0651887339736</v>
+        <v>475.2853265701005</v>
       </c>
       <c r="E5">
-        <v>-48.5</v>
+        <v>-43.39999999999999</v>
       </c>
       <c r="F5">
-        <v>15.3</v>
+        <v>20.4</v>
       </c>
       <c r="G5">
         <v>24.7</v>
@@ -1697,28 +1697,28 @@
         <v>39.6</v>
       </c>
       <c r="M5">
-        <v>0.7695899999999999</v>
+        <v>1.02612</v>
       </c>
       <c r="N5">
-        <v>38.83041</v>
+        <v>38.57388</v>
       </c>
       <c r="O5">
-        <v>10.4842107</v>
+        <v>10.4149476</v>
       </c>
       <c r="P5">
-        <v>28.3461993</v>
+        <v>28.1589324</v>
       </c>
       <c r="Q5">
-        <v>36.0461993</v>
+        <v>35.8589324</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09450428009763888</v>
+        <v>0.0948776599375849</v>
       </c>
       <c r="T5">
-        <v>0.8920359942249347</v>
+        <v>0.8988745771191299</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.45597006198106</v>
+        <v>38.59197754648579</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0925513135400815</v>
+        <v>0.0923319053854533</v>
       </c>
       <c r="C6">
-        <v>479.5853265701005</v>
+        <v>476.7264012813288</v>
       </c>
       <c r="D6">
-        <v>475.2853265701005</v>
+        <v>477.5264012813288</v>
       </c>
       <c r="E6">
-        <v>-43.39999999999999</v>
+        <v>-38.3</v>
       </c>
       <c r="F6">
-        <v>20.4</v>
+        <v>25.5</v>
       </c>
       <c r="G6">
         <v>24.7</v>
@@ -1779,28 +1779,28 @@
         <v>39.6</v>
       </c>
       <c r="M6">
-        <v>1.02612</v>
+        <v>1.28265</v>
       </c>
       <c r="N6">
-        <v>38.57388</v>
+        <v>38.31735</v>
       </c>
       <c r="O6">
-        <v>10.4149476</v>
+        <v>10.3456845</v>
       </c>
       <c r="P6">
-        <v>28.1589324</v>
+        <v>27.9716655</v>
       </c>
       <c r="Q6">
-        <v>35.8589324</v>
+        <v>35.6716655</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0948776599375849</v>
+        <v>0.09525890040574032</v>
       </c>
       <c r="T6">
-        <v>0.8988745771191299</v>
+        <v>0.9058571301795185</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.59197754648579</v>
+        <v>30.87358203718864</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0923319053854533</v>
+        <v>0.09211249723082511</v>
       </c>
       <c r="C7">
-        <v>476.7264012813288</v>
+        <v>473.8887104366563</v>
       </c>
       <c r="D7">
-        <v>477.5264012813288</v>
+        <v>479.7887104366563</v>
       </c>
       <c r="E7">
-        <v>-38.3</v>
+        <v>-33.2</v>
       </c>
       <c r="F7">
-        <v>25.5</v>
+        <v>30.6</v>
       </c>
       <c r="G7">
         <v>24.7</v>
@@ -1861,28 +1861,28 @@
         <v>39.6</v>
       </c>
       <c r="M7">
-        <v>1.28265</v>
+        <v>1.53918</v>
       </c>
       <c r="N7">
-        <v>38.31735</v>
+        <v>38.06082</v>
       </c>
       <c r="O7">
-        <v>10.3456845</v>
+        <v>10.2764214</v>
       </c>
       <c r="P7">
-        <v>27.9716655</v>
+        <v>27.7843986</v>
       </c>
       <c r="Q7">
-        <v>35.6716655</v>
+        <v>35.48439859999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09525890040574032</v>
+        <v>0.0956482523732182</v>
       </c>
       <c r="T7">
-        <v>0.9058571301795185</v>
+        <v>0.9129882481986389</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.87358203718864</v>
+        <v>25.72798503099053</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09211249723082511</v>
+        <v>0.09189308907619689</v>
       </c>
       <c r="C8">
-        <v>473.8887104366563</v>
+        <v>471.0725572709255</v>
       </c>
       <c r="D8">
-        <v>479.7887104366563</v>
+        <v>482.0725572709255</v>
       </c>
       <c r="E8">
-        <v>-33.2</v>
+        <v>-28.1</v>
       </c>
       <c r="F8">
-        <v>30.6</v>
+        <v>35.7</v>
       </c>
       <c r="G8">
         <v>24.7</v>
@@ -1943,28 +1943,28 @@
         <v>39.6</v>
       </c>
       <c r="M8">
-        <v>1.53918</v>
+        <v>1.79571</v>
       </c>
       <c r="N8">
-        <v>38.06082</v>
+        <v>37.80429</v>
       </c>
       <c r="O8">
-        <v>10.2764214</v>
+        <v>10.2071583</v>
       </c>
       <c r="P8">
-        <v>27.7843986</v>
+        <v>27.5971317</v>
       </c>
       <c r="Q8">
-        <v>35.48439859999999</v>
+        <v>35.29713169999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0956482523732182</v>
+        <v>0.09604597750128699</v>
       </c>
       <c r="T8">
-        <v>0.9129882481986389</v>
+        <v>0.9202727235945144</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.72798503099053</v>
+        <v>22.05255859799189</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09189308907619689</v>
+        <v>0.09167368092156869</v>
       </c>
       <c r="C9">
-        <v>471.0725572709255</v>
+        <v>468.2782508203171</v>
       </c>
       <c r="D9">
-        <v>482.0725572709255</v>
+        <v>484.3782508203171</v>
       </c>
       <c r="E9">
-        <v>-28.09999999999999</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="F9">
-        <v>35.7</v>
+        <v>40.8</v>
       </c>
       <c r="G9">
         <v>24.7</v>
@@ -2025,28 +2025,28 @@
         <v>39.6</v>
       </c>
       <c r="M9">
-        <v>1.79571</v>
+        <v>2.05224</v>
       </c>
       <c r="N9">
-        <v>37.80429</v>
+        <v>37.54776</v>
       </c>
       <c r="O9">
-        <v>10.2071583</v>
+        <v>10.1378952</v>
       </c>
       <c r="P9">
-        <v>27.5971317</v>
+        <v>27.4098648</v>
       </c>
       <c r="Q9">
-        <v>35.29713169999999</v>
+        <v>35.1098648</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09604597750128699</v>
+        <v>0.09645234882779205</v>
       </c>
       <c r="T9">
-        <v>0.9202727235945144</v>
+        <v>0.9277155571511699</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.05255859799188</v>
+        <v>19.29598877324289</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09167368092156869</v>
+        <v>0.09145427276694049</v>
       </c>
       <c r="C10">
-        <v>468.2782508203171</v>
+        <v>465.5061060617542</v>
       </c>
       <c r="D10">
-        <v>484.3782508203171</v>
+        <v>486.7061060617542</v>
       </c>
       <c r="E10">
-        <v>-22.99999999999999</v>
+        <v>-17.9</v>
       </c>
       <c r="F10">
-        <v>40.8</v>
+        <v>45.9</v>
       </c>
       <c r="G10">
         <v>24.7</v>
@@ -2107,28 +2107,28 @@
         <v>39.6</v>
       </c>
       <c r="M10">
-        <v>2.05224</v>
+        <v>2.30877</v>
       </c>
       <c r="N10">
-        <v>37.54776</v>
+        <v>37.29123</v>
       </c>
       <c r="O10">
-        <v>10.1378952</v>
+        <v>10.0686321</v>
       </c>
       <c r="P10">
-        <v>27.4098648</v>
+        <v>27.2225979</v>
       </c>
       <c r="Q10">
-        <v>35.1098648</v>
+        <v>34.92259789999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09645234882779205</v>
+        <v>0.09686765139224229</v>
       </c>
       <c r="T10">
-        <v>0.9277155571511699</v>
+        <v>0.9353219694673125</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.29598877324289</v>
+        <v>17.15199002066035</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09145427276694049</v>
+        <v>0.0912348646123123</v>
       </c>
       <c r="C11">
-        <v>465.5061060617542</v>
+        <v>462.7564440563424</v>
       </c>
       <c r="D11">
-        <v>486.7061060617542</v>
+        <v>489.0564440563423</v>
       </c>
       <c r="E11">
-        <v>-17.9</v>
+        <v>-12.8</v>
       </c>
       <c r="F11">
-        <v>45.9</v>
+        <v>50.99999999999999</v>
       </c>
       <c r="G11">
         <v>24.7</v>
@@ -2189,28 +2189,28 @@
         <v>39.6</v>
       </c>
       <c r="M11">
-        <v>2.30877</v>
+        <v>2.5653</v>
       </c>
       <c r="N11">
-        <v>37.29123</v>
+        <v>37.0347</v>
       </c>
       <c r="O11">
-        <v>10.0686321</v>
+        <v>9.999369000000002</v>
       </c>
       <c r="P11">
-        <v>27.2225979</v>
+        <v>27.035331</v>
       </c>
       <c r="Q11">
-        <v>34.92259789999999</v>
+        <v>34.735331</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09686765139224229</v>
+        <v>0.0972921829025692</v>
       </c>
       <c r="T11">
-        <v>0.9353219694673125</v>
+        <v>0.9430974131682581</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.15199002066035</v>
+        <v>15.43679101859432</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0912348646123123</v>
+        <v>0.09101545645768407</v>
       </c>
       <c r="C12">
-        <v>462.7564440563424</v>
+        <v>460.0295920969879</v>
       </c>
       <c r="D12">
-        <v>489.0564440563423</v>
+        <v>491.4295920969879</v>
       </c>
       <c r="E12">
-        <v>-12.8</v>
+        <v>-7.699999999999996</v>
       </c>
       <c r="F12">
-        <v>51</v>
+        <v>56.1</v>
       </c>
       <c r="G12">
         <v>24.7</v>
@@ -2271,28 +2271,28 @@
         <v>39.6</v>
       </c>
       <c r="M12">
-        <v>2.5653</v>
+        <v>2.82183</v>
       </c>
       <c r="N12">
-        <v>37.0347</v>
+        <v>36.77817</v>
       </c>
       <c r="O12">
-        <v>9.999369000000002</v>
+        <v>9.930105900000001</v>
       </c>
       <c r="P12">
-        <v>27.035331</v>
+        <v>26.8480641</v>
       </c>
       <c r="Q12">
-        <v>34.735331</v>
+        <v>34.5480641</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0972921829025692</v>
+        <v>0.09772625444683604</v>
       </c>
       <c r="T12">
-        <v>0.9430974131682581</v>
+        <v>0.951047585941135</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.43679101859432</v>
+        <v>14.03344638054029</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09101545645768407</v>
+        <v>0.09092744830305588</v>
       </c>
       <c r="C13">
-        <v>460.0295920969879</v>
+        <v>455.8879846752629</v>
       </c>
       <c r="D13">
-        <v>491.4295920969879</v>
+        <v>492.3879846752629</v>
       </c>
       <c r="E13">
-        <v>-7.699999999999996</v>
+        <v>-2.600000000000001</v>
       </c>
       <c r="F13">
-        <v>56.1</v>
+        <v>61.2</v>
       </c>
       <c r="G13">
         <v>24.7</v>
@@ -2353,45 +2353,45 @@
         <v>39.6</v>
       </c>
       <c r="M13">
-        <v>2.82183</v>
+        <v>3.17016</v>
       </c>
       <c r="N13">
-        <v>36.77817</v>
+        <v>36.42984</v>
       </c>
       <c r="O13">
-        <v>9.930105900000001</v>
+        <v>9.8360568</v>
       </c>
       <c r="P13">
-        <v>26.8480641</v>
+        <v>26.5937832</v>
       </c>
       <c r="Q13">
-        <v>34.5480641</v>
+        <v>34.29378319999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09772625444683604</v>
+        <v>0.09817019125347259</v>
       </c>
       <c r="T13">
-        <v>0.951047585941135</v>
+        <v>0.9591784444588503</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>14.03344638054029</v>
+        <v>12.49148307971837</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09092744830305588</v>
+        <v>0.09071899014842766</v>
       </c>
       <c r="C14">
-        <v>455.8879846752629</v>
+        <v>453.0730380637596</v>
       </c>
       <c r="D14">
-        <v>492.3879846752629</v>
+        <v>494.6730380637596</v>
       </c>
       <c r="E14">
-        <v>-2.600000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="F14">
-        <v>61.2</v>
+        <v>66.3</v>
       </c>
       <c r="G14">
         <v>24.7</v>
@@ -2435,28 +2435,28 @@
         <v>39.6</v>
       </c>
       <c r="M14">
-        <v>3.17016</v>
+        <v>3.43434</v>
       </c>
       <c r="N14">
-        <v>36.42984</v>
+        <v>36.16566</v>
       </c>
       <c r="O14">
-        <v>9.8360568</v>
+        <v>9.764728200000002</v>
       </c>
       <c r="P14">
-        <v>26.5937832</v>
+        <v>26.4009318</v>
       </c>
       <c r="Q14">
-        <v>34.29378319999999</v>
+        <v>34.1009318</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09817019125347259</v>
+        <v>0.09862433350393984</v>
       </c>
       <c r="T14">
-        <v>0.9591784444588503</v>
+        <v>0.9674962192643288</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.49148307971837</v>
+        <v>11.53059976589389</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09071899014842766</v>
+        <v>0.09051053199379946</v>
       </c>
       <c r="C15">
-        <v>453.0730380637596</v>
+        <v>450.2793990946101</v>
       </c>
       <c r="D15">
-        <v>494.6730380637596</v>
+        <v>496.97939909461</v>
       </c>
       <c r="E15">
-        <v>2.5</v>
+        <v>7.600000000000009</v>
       </c>
       <c r="F15">
-        <v>66.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G15">
         <v>24.7</v>
@@ -2517,28 +2517,28 @@
         <v>39.6</v>
       </c>
       <c r="M15">
-        <v>3.43434</v>
+        <v>3.69852</v>
       </c>
       <c r="N15">
-        <v>36.16566</v>
+        <v>35.90148</v>
       </c>
       <c r="O15">
-        <v>9.764728200000002</v>
+        <v>9.693399600000001</v>
       </c>
       <c r="P15">
-        <v>26.4009318</v>
+        <v>26.2080804</v>
       </c>
       <c r="Q15">
-        <v>34.1009318</v>
+        <v>33.9080804</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09862433350393984</v>
+        <v>0.0990890372020924</v>
       </c>
       <c r="T15">
-        <v>0.9674962192643288</v>
+        <v>0.9760074306931907</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.53059976589389</v>
+        <v>10.70698549690146</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09051053199379946</v>
+        <v>0.09030207383917126</v>
       </c>
       <c r="C16">
-        <v>450.2793990946101</v>
+        <v>447.5073671978024</v>
       </c>
       <c r="D16">
-        <v>496.97939909461</v>
+        <v>499.3073671978024</v>
       </c>
       <c r="E16">
-        <v>7.600000000000009</v>
+        <v>12.70000000000002</v>
       </c>
       <c r="F16">
-        <v>71.40000000000001</v>
+        <v>76.50000000000001</v>
       </c>
       <c r="G16">
         <v>24.7</v>
@@ -2599,28 +2599,28 @@
         <v>39.6</v>
       </c>
       <c r="M16">
-        <v>3.69852</v>
+        <v>3.962700000000001</v>
       </c>
       <c r="N16">
-        <v>35.90148</v>
+        <v>35.6373</v>
       </c>
       <c r="O16">
-        <v>9.693399600000001</v>
+        <v>9.622071000000002</v>
       </c>
       <c r="P16">
-        <v>26.2080804</v>
+        <v>26.015229</v>
       </c>
       <c r="Q16">
-        <v>33.9080804</v>
+        <v>33.71522899999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0990890372020924</v>
+        <v>0.09956467510490737</v>
       </c>
       <c r="T16">
-        <v>0.9760074306931907</v>
+        <v>0.9847189059203788</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.70698549690146</v>
+        <v>9.993186463774698</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09030207383917126</v>
+        <v>0.09029217568454305</v>
       </c>
       <c r="C17">
-        <v>447.5073671978024</v>
+        <v>442.5184478867435</v>
       </c>
       <c r="D17">
-        <v>499.3073671978024</v>
+        <v>499.4184478867435</v>
       </c>
       <c r="E17">
-        <v>12.7</v>
+        <v>17.80000000000001</v>
       </c>
       <c r="F17">
-        <v>76.5</v>
+        <v>81.60000000000001</v>
       </c>
       <c r="G17">
         <v>24.7</v>
@@ -2681,45 +2681,45 @@
         <v>39.6</v>
       </c>
       <c r="M17">
-        <v>3.9627</v>
+        <v>4.365600000000001</v>
       </c>
       <c r="N17">
-        <v>35.6373</v>
+        <v>35.2344</v>
       </c>
       <c r="O17">
-        <v>9.622071000000002</v>
+        <v>9.513288000000001</v>
       </c>
       <c r="P17">
-        <v>26.015229</v>
+        <v>25.721112</v>
       </c>
       <c r="Q17">
-        <v>33.71522899999999</v>
+        <v>33.42111199999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09956467510490737</v>
+        <v>0.1000516377196941</v>
       </c>
       <c r="T17">
-        <v>0.9847189059203788</v>
+        <v>0.9936377972244047</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>9.9931864637747</v>
+        <v>9.070918086860912</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09029217568454305</v>
+        <v>0.09009612752991486</v>
       </c>
       <c r="C18">
-        <v>442.5184478867435</v>
+        <v>439.6288005869732</v>
       </c>
       <c r="D18">
-        <v>499.4184478867435</v>
+        <v>501.6288005869732</v>
       </c>
       <c r="E18">
-        <v>17.80000000000001</v>
+        <v>22.90000000000001</v>
       </c>
       <c r="F18">
-        <v>81.60000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="G18">
         <v>24.7</v>
@@ -2763,28 +2763,28 @@
         <v>39.6</v>
       </c>
       <c r="M18">
-        <v>4.365600000000001</v>
+        <v>4.63845</v>
       </c>
       <c r="N18">
-        <v>35.2344</v>
+        <v>34.96155</v>
       </c>
       <c r="O18">
-        <v>9.513288000000001</v>
+        <v>9.439618500000002</v>
       </c>
       <c r="P18">
-        <v>25.721112</v>
+        <v>25.5219315</v>
       </c>
       <c r="Q18">
-        <v>33.42111199999999</v>
+        <v>33.2219315</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1000516377196941</v>
+        <v>0.1005503343733914</v>
       </c>
       <c r="T18">
-        <v>0.9936377972244047</v>
+        <v>1.002771601571901</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.070918086860912</v>
+        <v>8.537334669986741</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09009612752991486</v>
+        <v>0.08990007937528664</v>
       </c>
       <c r="C19">
-        <v>439.6288005869732</v>
+        <v>436.7588056585413</v>
       </c>
       <c r="D19">
-        <v>501.6288005869732</v>
+        <v>503.8588056585413</v>
       </c>
       <c r="E19">
-        <v>22.90000000000001</v>
+        <v>28.00000000000001</v>
       </c>
       <c r="F19">
-        <v>86.7</v>
+        <v>91.80000000000001</v>
       </c>
       <c r="G19">
         <v>24.7</v>
@@ -2845,28 +2845,28 @@
         <v>39.6</v>
       </c>
       <c r="M19">
-        <v>4.63845</v>
+        <v>4.911300000000001</v>
       </c>
       <c r="N19">
-        <v>34.96155</v>
+        <v>34.6887</v>
       </c>
       <c r="O19">
-        <v>9.439618500000002</v>
+        <v>9.365949000000001</v>
       </c>
       <c r="P19">
-        <v>25.5219315</v>
+        <v>25.322751</v>
       </c>
       <c r="Q19">
-        <v>33.2219315</v>
+        <v>33.02275099999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1005503343733914</v>
+        <v>0.1010611943601057</v>
       </c>
       <c r="T19">
-        <v>1.002771601571901</v>
+        <v>1.01212818163519</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.537334669986741</v>
+        <v>8.06303829943192</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08990007937528666</v>
+        <v>0.08970403122065844</v>
       </c>
       <c r="C20">
-        <v>436.7588056585411</v>
+        <v>433.9087263673269</v>
       </c>
       <c r="D20">
-        <v>503.8588056585411</v>
+        <v>506.1087263673269</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>33.10000000000001</v>
       </c>
       <c r="F20">
-        <v>91.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G20">
         <v>24.7</v>
@@ -2927,28 +2927,28 @@
         <v>39.6</v>
       </c>
       <c r="M20">
-        <v>4.9113</v>
+        <v>5.18415</v>
       </c>
       <c r="N20">
-        <v>34.6887</v>
+        <v>34.41585</v>
       </c>
       <c r="O20">
-        <v>9.365949000000002</v>
+        <v>9.292279500000001</v>
       </c>
       <c r="P20">
-        <v>25.322751</v>
+        <v>25.1235705</v>
       </c>
       <c r="Q20">
-        <v>33.022751</v>
+        <v>32.8235705</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1010611943601057</v>
+        <v>0.1015846681736524</v>
       </c>
       <c r="T20">
-        <v>1.01212818163519</v>
+        <v>1.021715788366708</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.063038299431923</v>
+        <v>7.638667862619716</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08970403122065844</v>
+        <v>0.08962478306603024</v>
       </c>
       <c r="C21">
-        <v>433.9087263673269</v>
+        <v>429.7239204607104</v>
       </c>
       <c r="D21">
-        <v>506.1087263673269</v>
+        <v>507.0239204607103</v>
       </c>
       <c r="E21">
-        <v>33.10000000000001</v>
+        <v>38.2</v>
       </c>
       <c r="F21">
-        <v>96.90000000000001</v>
+        <v>102</v>
       </c>
       <c r="G21">
         <v>24.7</v>
@@ -3009,45 +3009,45 @@
         <v>39.6</v>
       </c>
       <c r="M21">
-        <v>5.18415</v>
+        <v>5.5386</v>
       </c>
       <c r="N21">
-        <v>34.41585</v>
+        <v>34.0614</v>
       </c>
       <c r="O21">
-        <v>9.292279500000001</v>
+        <v>9.196578000000001</v>
       </c>
       <c r="P21">
-        <v>25.1235705</v>
+        <v>24.864822</v>
       </c>
       <c r="Q21">
-        <v>32.8235705</v>
+        <v>32.56482199999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1015846681736524</v>
+        <v>0.1021212288325378</v>
       </c>
       <c r="T21">
-        <v>1.021715788366708</v>
+        <v>1.031543085266515</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.27</v>
       </c>
       <c r="W21">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.638667862619716</v>
+        <v>7.149821254468638</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08962478306603024</v>
+        <v>0.08943457491140203</v>
       </c>
       <c r="C22">
-        <v>429.7239204607104</v>
+        <v>426.8340963237503</v>
       </c>
       <c r="D22">
-        <v>507.0239204607103</v>
+        <v>509.2340963237502</v>
       </c>
       <c r="E22">
-        <v>38.2</v>
+        <v>43.30000000000001</v>
       </c>
       <c r="F22">
-        <v>102</v>
+        <v>107.1</v>
       </c>
       <c r="G22">
         <v>24.7</v>
@@ -3091,28 +3091,28 @@
         <v>39.6</v>
       </c>
       <c r="M22">
-        <v>5.5386</v>
+        <v>5.815530000000001</v>
       </c>
       <c r="N22">
-        <v>34.0614</v>
+        <v>33.78447</v>
       </c>
       <c r="O22">
-        <v>9.196578000000001</v>
+        <v>9.121806900000001</v>
       </c>
       <c r="P22">
-        <v>24.864822</v>
+        <v>24.6626631</v>
       </c>
       <c r="Q22">
-        <v>32.56482199999999</v>
+        <v>32.36266309999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1021212288325378</v>
+        <v>0.1026713733055722</v>
       </c>
       <c r="T22">
-        <v>1.031543085266515</v>
+        <v>1.041619174492898</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.149821254468638</v>
+        <v>6.809353575684416</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08943457491140203</v>
+        <v>0.08924436675677384</v>
       </c>
       <c r="C23">
-        <v>426.8340963237503</v>
+        <v>423.9636253735757</v>
       </c>
       <c r="D23">
-        <v>509.2340963237502</v>
+        <v>511.4636253735756</v>
       </c>
       <c r="E23">
-        <v>43.3</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="F23">
-        <v>107.1</v>
+        <v>112.2</v>
       </c>
       <c r="G23">
         <v>24.7</v>
@@ -3173,28 +3173,28 @@
         <v>39.6</v>
       </c>
       <c r="M23">
-        <v>5.81553</v>
+        <v>6.09246</v>
       </c>
       <c r="N23">
-        <v>33.78447</v>
+        <v>33.50754</v>
       </c>
       <c r="O23">
-        <v>9.121806900000001</v>
+        <v>9.0470358</v>
       </c>
       <c r="P23">
-        <v>24.6626631</v>
+        <v>24.4605042</v>
       </c>
       <c r="Q23">
-        <v>32.36266309999999</v>
+        <v>32.16050419999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1026713733055722</v>
+        <v>0.1032356240471459</v>
       </c>
       <c r="T23">
-        <v>1.041619174492898</v>
+        <v>1.051953624981497</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.809353575684417</v>
+        <v>6.499837504062398</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08924436675677384</v>
+        <v>0.08905415860214562</v>
       </c>
       <c r="C24">
-        <v>423.9636253735757</v>
+        <v>421.1127629244085</v>
       </c>
       <c r="D24">
-        <v>511.4636253735756</v>
+        <v>513.7127629244085</v>
       </c>
       <c r="E24">
-        <v>48.40000000000001</v>
+        <v>53.50000000000001</v>
       </c>
       <c r="F24">
-        <v>112.2</v>
+        <v>117.3</v>
       </c>
       <c r="G24">
         <v>24.7</v>
@@ -3255,28 +3255,28 @@
         <v>39.6</v>
       </c>
       <c r="M24">
-        <v>6.09246</v>
+        <v>6.369390000000001</v>
       </c>
       <c r="N24">
-        <v>33.50754</v>
+        <v>33.23061</v>
       </c>
       <c r="O24">
-        <v>9.0470358</v>
+        <v>8.9722647</v>
       </c>
       <c r="P24">
-        <v>24.4605042</v>
+        <v>24.2583453</v>
       </c>
       <c r="Q24">
-        <v>32.16050419999999</v>
+        <v>31.95834529999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1032356240471459</v>
+        <v>0.1038145306521372</v>
       </c>
       <c r="T24">
-        <v>1.051953624981497</v>
+        <v>1.062556502755513</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.499837504062398</v>
+        <v>6.217235873450988</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08905415860214562</v>
+        <v>0.08903915044751741</v>
       </c>
       <c r="C25">
-        <v>421.1127629244085</v>
+        <v>416.1910707889401</v>
       </c>
       <c r="D25">
-        <v>513.7127629244085</v>
+        <v>513.8910707889401</v>
       </c>
       <c r="E25">
-        <v>53.50000000000001</v>
+        <v>58.60000000000001</v>
       </c>
       <c r="F25">
-        <v>117.3</v>
+        <v>122.4</v>
       </c>
       <c r="G25">
         <v>24.7</v>
@@ -3337,45 +3337,45 @@
         <v>39.6</v>
       </c>
       <c r="M25">
-        <v>6.369390000000001</v>
+        <v>6.768720000000001</v>
       </c>
       <c r="N25">
-        <v>33.23061</v>
+        <v>32.83128</v>
       </c>
       <c r="O25">
-        <v>8.9722647</v>
+        <v>8.8644456</v>
       </c>
       <c r="P25">
-        <v>24.2583453</v>
+        <v>23.9668344</v>
       </c>
       <c r="Q25">
-        <v>31.95834529999999</v>
+        <v>31.6668344</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1038145306521372</v>
+        <v>0.1044086716414703</v>
       </c>
       <c r="T25">
-        <v>1.062556502755513</v>
+        <v>1.073438403628846</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.217235873450988</v>
+        <v>5.850441442399744</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08903915044751741</v>
+        <v>0.0888562422928892</v>
       </c>
       <c r="C26">
-        <v>416.1910707889401</v>
+        <v>413.2741425674413</v>
       </c>
       <c r="D26">
-        <v>513.8910707889401</v>
+        <v>516.0741425674413</v>
       </c>
       <c r="E26">
-        <v>58.59999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="F26">
-        <v>122.4</v>
+        <v>127.5</v>
       </c>
       <c r="G26">
         <v>24.7</v>
@@ -3419,28 +3419,28 @@
         <v>39.6</v>
       </c>
       <c r="M26">
-        <v>6.76872</v>
+        <v>7.05075</v>
       </c>
       <c r="N26">
-        <v>32.83128</v>
+        <v>32.54925</v>
       </c>
       <c r="O26">
-        <v>8.8644456</v>
+        <v>8.788297500000001</v>
       </c>
       <c r="P26">
-        <v>23.9668344</v>
+        <v>23.7609525</v>
       </c>
       <c r="Q26">
-        <v>31.6668344</v>
+        <v>31.4609525</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1044086716414703</v>
+        <v>0.1050186563905189</v>
       </c>
       <c r="T26">
-        <v>1.073438403628846</v>
+        <v>1.084610488525468</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.850441442399744</v>
+        <v>5.616423784703755</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0888562422928892</v>
+        <v>0.08867333413826099</v>
       </c>
       <c r="C27">
-        <v>413.2741425674413</v>
+        <v>410.3758413847979</v>
       </c>
       <c r="D27">
-        <v>516.0741425674413</v>
+        <v>518.2758413847979</v>
       </c>
       <c r="E27">
-        <v>63.7</v>
+        <v>68.8</v>
       </c>
       <c r="F27">
-        <v>127.5</v>
+        <v>132.6</v>
       </c>
       <c r="G27">
         <v>24.7</v>
@@ -3501,28 +3501,28 @@
         <v>39.6</v>
       </c>
       <c r="M27">
-        <v>7.05075</v>
+        <v>7.33278</v>
       </c>
       <c r="N27">
-        <v>32.54925</v>
+        <v>32.26722</v>
       </c>
       <c r="O27">
-        <v>8.788297500000001</v>
+        <v>8.712149400000001</v>
       </c>
       <c r="P27">
-        <v>23.7609525</v>
+        <v>23.5550706</v>
       </c>
       <c r="Q27">
-        <v>31.4609525</v>
+        <v>31.2550706</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1050186563905189</v>
+        <v>0.1056451272138662</v>
       </c>
       <c r="T27">
-        <v>1.084610488525468</v>
+        <v>1.096084521662539</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.616423784703755</v>
+        <v>5.400407485292073</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08867333413826099</v>
+        <v>0.0884904259836328</v>
       </c>
       <c r="C28">
-        <v>410.3758413847979</v>
+        <v>407.4964066649948</v>
       </c>
       <c r="D28">
-        <v>518.2758413847979</v>
+        <v>520.4964066649948</v>
       </c>
       <c r="E28">
-        <v>68.8</v>
+        <v>73.90000000000002</v>
       </c>
       <c r="F28">
-        <v>132.6</v>
+        <v>137.7</v>
       </c>
       <c r="G28">
         <v>24.7</v>
@@ -3583,28 +3583,28 @@
         <v>39.6</v>
       </c>
       <c r="M28">
-        <v>7.33278</v>
+        <v>7.614810000000001</v>
       </c>
       <c r="N28">
-        <v>32.26722</v>
+        <v>31.98519</v>
       </c>
       <c r="O28">
-        <v>8.712149400000001</v>
+        <v>8.6360013</v>
       </c>
       <c r="P28">
-        <v>23.5550706</v>
+        <v>23.3491887</v>
       </c>
       <c r="Q28">
-        <v>31.2550706</v>
+        <v>31.04918869999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1056451272138662</v>
+        <v>0.1062887616214148</v>
       </c>
       <c r="T28">
-        <v>1.096084521662539</v>
+        <v>1.107872911871859</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.400407485292073</v>
+        <v>5.200392393244217</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0884904259836328</v>
+        <v>0.08830751782900459</v>
       </c>
       <c r="C29">
-        <v>407.4964066649948</v>
+        <v>404.6360819529446</v>
       </c>
       <c r="D29">
-        <v>520.4964066649948</v>
+        <v>522.7360819529446</v>
       </c>
       <c r="E29">
-        <v>73.90000000000002</v>
+        <v>79.00000000000001</v>
       </c>
       <c r="F29">
-        <v>137.7</v>
+        <v>142.8</v>
       </c>
       <c r="G29">
         <v>24.7</v>
@@ -3665,28 +3665,28 @@
         <v>39.6</v>
       </c>
       <c r="M29">
-        <v>7.614810000000001</v>
+        <v>7.896840000000001</v>
       </c>
       <c r="N29">
-        <v>31.98519</v>
+        <v>31.70316</v>
       </c>
       <c r="O29">
-        <v>8.6360013</v>
+        <v>8.559853200000001</v>
       </c>
       <c r="P29">
-        <v>23.3491887</v>
+        <v>23.1433068</v>
       </c>
       <c r="Q29">
-        <v>31.04918869999999</v>
+        <v>30.84330679999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1062887616214148</v>
+        <v>0.1069502747625064</v>
       </c>
       <c r="T29">
-        <v>1.107872911871859</v>
+        <v>1.119988757364771</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.200392393244217</v>
+        <v>5.014664093485495</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08830751782900459</v>
+        <v>0.08812460967437639</v>
       </c>
       <c r="C30">
-        <v>404.6360819529446</v>
+        <v>401.7951150035311</v>
       </c>
       <c r="D30">
-        <v>522.7360819529446</v>
+        <v>524.9951150035311</v>
       </c>
       <c r="E30">
-        <v>79.00000000000001</v>
+        <v>84.10000000000001</v>
       </c>
       <c r="F30">
-        <v>142.8</v>
+        <v>147.9</v>
       </c>
       <c r="G30">
         <v>24.7</v>
@@ -3747,28 +3747,28 @@
         <v>39.6</v>
       </c>
       <c r="M30">
-        <v>7.896840000000001</v>
+        <v>8.17887</v>
       </c>
       <c r="N30">
-        <v>31.70316</v>
+        <v>31.42113</v>
       </c>
       <c r="O30">
-        <v>8.559853200000001</v>
+        <v>8.483705100000002</v>
       </c>
       <c r="P30">
-        <v>23.1433068</v>
+        <v>22.9374249</v>
       </c>
       <c r="Q30">
-        <v>30.84330679999999</v>
+        <v>30.6374249</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1069502747625064</v>
+        <v>0.1076304220765865</v>
       </c>
       <c r="T30">
-        <v>1.119988757364771</v>
+        <v>1.132445894280018</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.014664093485495</v>
+        <v>4.841744641985995</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08812460967437639</v>
+        <v>0.0879417015197482</v>
       </c>
       <c r="C31">
-        <v>401.7951150035311</v>
+        <v>398.9737578729728</v>
       </c>
       <c r="D31">
-        <v>524.9951150035311</v>
+        <v>527.2737578729727</v>
       </c>
       <c r="E31">
-        <v>84.09999999999998</v>
+        <v>89.2</v>
       </c>
       <c r="F31">
-        <v>147.9</v>
+        <v>153</v>
       </c>
       <c r="G31">
         <v>24.7</v>
@@ -3829,28 +3829,28 @@
         <v>39.6</v>
       </c>
       <c r="M31">
-        <v>8.17887</v>
+        <v>8.460900000000001</v>
       </c>
       <c r="N31">
-        <v>31.42113</v>
+        <v>31.1391</v>
       </c>
       <c r="O31">
-        <v>8.483705100000002</v>
+        <v>8.407557000000001</v>
       </c>
       <c r="P31">
-        <v>22.9374249</v>
+        <v>22.731543</v>
       </c>
       <c r="Q31">
-        <v>30.6374249</v>
+        <v>30.43154299999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1076304220765865</v>
+        <v>0.1083300021710689</v>
       </c>
       <c r="T31">
-        <v>1.132445894280018</v>
+        <v>1.145258949392844</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.841744641985995</v>
+        <v>4.680353153919795</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0879417015197482</v>
+        <v>0.08775879336511999</v>
       </c>
       <c r="C32">
-        <v>398.9737578729728</v>
+        <v>396.1722670125754</v>
       </c>
       <c r="D32">
-        <v>527.2737578729727</v>
+        <v>529.5722670125754</v>
       </c>
       <c r="E32">
-        <v>89.2</v>
+        <v>94.3</v>
       </c>
       <c r="F32">
-        <v>153</v>
+        <v>158.1</v>
       </c>
       <c r="G32">
         <v>24.7</v>
@@ -3911,28 +3911,28 @@
         <v>39.6</v>
       </c>
       <c r="M32">
-        <v>8.460900000000001</v>
+        <v>8.742929999999999</v>
       </c>
       <c r="N32">
-        <v>31.1391</v>
+        <v>30.85707</v>
       </c>
       <c r="O32">
-        <v>8.407557000000001</v>
+        <v>8.331408900000001</v>
       </c>
       <c r="P32">
-        <v>22.731543</v>
+        <v>22.5256611</v>
       </c>
       <c r="Q32">
-        <v>30.43154299999999</v>
+        <v>30.2256611</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1083300021710689</v>
+        <v>0.1090498599494493</v>
       </c>
       <c r="T32">
-        <v>1.145258949392844</v>
+        <v>1.158443397407491</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.680353153919795</v>
+        <v>4.529374019922383</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08775879336511999</v>
+        <v>0.08815988521049178</v>
       </c>
       <c r="C33">
-        <v>396.1722670125754</v>
+        <v>386.0579210865105</v>
       </c>
       <c r="D33">
-        <v>529.5722670125754</v>
+        <v>524.5579210865105</v>
       </c>
       <c r="E33">
-        <v>94.3</v>
+        <v>99.40000000000002</v>
       </c>
       <c r="F33">
-        <v>158.1</v>
+        <v>163.2</v>
       </c>
       <c r="G33">
         <v>24.7</v>
@@ -3993,45 +3993,45 @@
         <v>39.6</v>
       </c>
       <c r="M33">
-        <v>8.742929999999999</v>
+        <v>9.432960000000001</v>
       </c>
       <c r="N33">
-        <v>30.85707</v>
+        <v>30.16704</v>
       </c>
       <c r="O33">
-        <v>8.331408900000001</v>
+        <v>8.1451008</v>
       </c>
       <c r="P33">
-        <v>22.5256611</v>
+        <v>22.0219392</v>
       </c>
       <c r="Q33">
-        <v>30.2256611</v>
+        <v>29.72193919999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1090498599494493</v>
+        <v>0.1097908900154291</v>
       </c>
       <c r="T33">
-        <v>1.158443397407491</v>
+        <v>1.172015623304922</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.529374019922383</v>
+        <v>4.198046000407083</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08815988521049178</v>
+        <v>0.08799522705586357</v>
       </c>
       <c r="C34">
-        <v>386.0579210865105</v>
+        <v>383.0048999821891</v>
       </c>
       <c r="D34">
-        <v>524.5579210865105</v>
+        <v>526.6048999821891</v>
       </c>
       <c r="E34">
-        <v>99.40000000000002</v>
+        <v>104.5</v>
       </c>
       <c r="F34">
-        <v>163.2</v>
+        <v>168.3</v>
       </c>
       <c r="G34">
         <v>24.7</v>
@@ -4075,28 +4075,28 @@
         <v>39.6</v>
       </c>
       <c r="M34">
-        <v>9.432960000000001</v>
+        <v>9.727740000000001</v>
       </c>
       <c r="N34">
-        <v>30.16704</v>
+        <v>29.87226</v>
       </c>
       <c r="O34">
-        <v>8.1451008</v>
+        <v>8.0655102</v>
       </c>
       <c r="P34">
-        <v>22.0219392</v>
+        <v>21.8067498</v>
       </c>
       <c r="Q34">
-        <v>29.72193919999999</v>
+        <v>29.50674979999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1097908900154291</v>
+        <v>0.1105540403818859</v>
       </c>
       <c r="T34">
-        <v>1.172015623304922</v>
+        <v>1.185992990273918</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.198046000407083</v>
+        <v>4.070832485243232</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08799522705586357</v>
+        <v>0.08869926890123536</v>
       </c>
       <c r="C35">
-        <v>383.0048999821891</v>
+        <v>369.2625176045583</v>
       </c>
       <c r="D35">
-        <v>526.6048999821891</v>
+        <v>517.9625176045582</v>
       </c>
       <c r="E35">
-        <v>104.5</v>
+        <v>109.6</v>
       </c>
       <c r="F35">
-        <v>168.3</v>
+        <v>173.4</v>
       </c>
       <c r="G35">
         <v>24.7</v>
@@ -4157,45 +4157,45 @@
         <v>39.6</v>
       </c>
       <c r="M35">
-        <v>9.727740000000001</v>
+        <v>10.62942</v>
       </c>
       <c r="N35">
-        <v>29.87226</v>
+        <v>28.97058</v>
       </c>
       <c r="O35">
-        <v>8.0655102</v>
+        <v>7.822056600000001</v>
       </c>
       <c r="P35">
-        <v>21.8067498</v>
+        <v>21.1485234</v>
       </c>
       <c r="Q35">
-        <v>29.50674979999999</v>
+        <v>28.8485234</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1105540403818859</v>
+        <v>0.1113403165170233</v>
       </c>
       <c r="T35">
-        <v>1.185992990273918</v>
+        <v>1.200393913817731</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.070832485243232</v>
+        <v>3.725509011780511</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08869926890123536</v>
+        <v>0.08856016074660715</v>
       </c>
       <c r="C36">
-        <v>369.2625176045583</v>
+        <v>365.8475629536048</v>
       </c>
       <c r="D36">
-        <v>517.9625176045582</v>
+        <v>519.6475629536047</v>
       </c>
       <c r="E36">
-        <v>109.6</v>
+        <v>114.7</v>
       </c>
       <c r="F36">
-        <v>173.4</v>
+        <v>178.5</v>
       </c>
       <c r="G36">
         <v>24.7</v>
@@ -4239,28 +4239,28 @@
         <v>39.6</v>
       </c>
       <c r="M36">
-        <v>10.62942</v>
+        <v>10.94205</v>
       </c>
       <c r="N36">
-        <v>28.97058</v>
+        <v>28.65795</v>
       </c>
       <c r="O36">
-        <v>7.822056600000001</v>
+        <v>7.7376465</v>
       </c>
       <c r="P36">
-        <v>21.1485234</v>
+        <v>20.9203035</v>
       </c>
       <c r="Q36">
-        <v>28.8485234</v>
+        <v>28.6203035</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1113403165170233</v>
+        <v>0.112150785764011</v>
       </c>
       <c r="T36">
-        <v>1.200393913817731</v>
+        <v>1.215237942701355</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.725509011780511</v>
+        <v>3.61906589715821</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08856016074660715</v>
+        <v>0.08842105259197894</v>
       </c>
       <c r="C37">
-        <v>365.8475629536048</v>
+        <v>362.4436077282738</v>
       </c>
       <c r="D37">
-        <v>519.6475629536047</v>
+        <v>521.3436077282738</v>
       </c>
       <c r="E37">
-        <v>114.7</v>
+        <v>119.8</v>
       </c>
       <c r="F37">
-        <v>178.5</v>
+        <v>183.6</v>
       </c>
       <c r="G37">
         <v>24.7</v>
@@ -4321,28 +4321,28 @@
         <v>39.6</v>
       </c>
       <c r="M37">
-        <v>10.94205</v>
+        <v>11.25468</v>
       </c>
       <c r="N37">
-        <v>28.65795</v>
+        <v>28.34532</v>
       </c>
       <c r="O37">
-        <v>7.7376465</v>
+        <v>7.653236400000001</v>
       </c>
       <c r="P37">
-        <v>20.9203035</v>
+        <v>20.6920836</v>
       </c>
       <c r="Q37">
-        <v>28.6203035</v>
+        <v>28.3920836</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.112150785764011</v>
+        <v>0.1129865821749671</v>
       </c>
       <c r="T37">
-        <v>1.215237942701355</v>
+        <v>1.230545847487592</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.61906589715821</v>
+        <v>3.518536288903816</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08842105259197895</v>
+        <v>0.08903822443735077</v>
       </c>
       <c r="C38">
-        <v>362.4436077282737</v>
+        <v>349.9020765219989</v>
       </c>
       <c r="D38">
-        <v>521.3436077282737</v>
+        <v>513.9020765219989</v>
       </c>
       <c r="E38">
-        <v>119.8</v>
+        <v>124.9</v>
       </c>
       <c r="F38">
-        <v>183.6</v>
+        <v>188.7</v>
       </c>
       <c r="G38">
         <v>24.7</v>
@@ -4403,45 +4403,45 @@
         <v>39.6</v>
       </c>
       <c r="M38">
-        <v>11.25468</v>
+        <v>12.09567</v>
       </c>
       <c r="N38">
-        <v>28.34532</v>
+        <v>27.50433</v>
       </c>
       <c r="O38">
-        <v>7.653236400000001</v>
+        <v>7.426169100000001</v>
       </c>
       <c r="P38">
-        <v>20.6920836</v>
+        <v>20.0781609</v>
       </c>
       <c r="Q38">
-        <v>28.3920836</v>
+        <v>27.7781609</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1129865821749671</v>
+        <v>0.1138489118053187</v>
       </c>
       <c r="T38">
-        <v>1.230545847487592</v>
+        <v>1.246339717505137</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.518536288903816</v>
+        <v>3.273898841486251</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08903822443735077</v>
+        <v>0.08891955628272255</v>
       </c>
       <c r="C39">
-        <v>349.9020765219989</v>
+        <v>346.2163724085479</v>
       </c>
       <c r="D39">
-        <v>513.9020765219989</v>
+        <v>515.3163724085479</v>
       </c>
       <c r="E39">
-        <v>124.9</v>
+        <v>130</v>
       </c>
       <c r="F39">
-        <v>188.7</v>
+        <v>193.8</v>
       </c>
       <c r="G39">
         <v>24.7</v>
@@ -4485,28 +4485,28 @@
         <v>39.6</v>
       </c>
       <c r="M39">
-        <v>12.09567</v>
+        <v>12.42258</v>
       </c>
       <c r="N39">
-        <v>27.50433</v>
+        <v>27.17742</v>
       </c>
       <c r="O39">
-        <v>7.426169100000001</v>
+        <v>7.3379034</v>
       </c>
       <c r="P39">
-        <v>20.0781609</v>
+        <v>19.8395166</v>
       </c>
       <c r="Q39">
-        <v>27.7781609</v>
+        <v>27.53951659999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1138489118053187</v>
+        <v>0.1147390585205202</v>
       </c>
       <c r="T39">
-        <v>1.246339717505137</v>
+        <v>1.262643067200668</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.273898841486251</v>
+        <v>3.18774360881556</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08891955628272255</v>
+        <v>0.08880088812809435</v>
       </c>
       <c r="C40">
-        <v>346.2163724085479</v>
+        <v>342.5384742679621</v>
       </c>
       <c r="D40">
-        <v>515.3163724085479</v>
+        <v>516.738474267962</v>
       </c>
       <c r="E40">
-        <v>130</v>
+        <v>135.1</v>
       </c>
       <c r="F40">
-        <v>193.8</v>
+        <v>198.9</v>
       </c>
       <c r="G40">
         <v>24.7</v>
@@ -4567,28 +4567,28 @@
         <v>39.6</v>
       </c>
       <c r="M40">
-        <v>12.42258</v>
+        <v>12.74949</v>
       </c>
       <c r="N40">
-        <v>27.17742</v>
+        <v>26.85051</v>
       </c>
       <c r="O40">
-        <v>7.3379034</v>
+        <v>7.2496377</v>
       </c>
       <c r="P40">
-        <v>19.8395166</v>
+        <v>19.6008723</v>
       </c>
       <c r="Q40">
-        <v>27.53951659999999</v>
+        <v>27.30087229999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1147390585205202</v>
+        <v>0.1156583903739252</v>
       </c>
       <c r="T40">
-        <v>1.262643067200668</v>
+        <v>1.279480952951791</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.18774360881556</v>
+        <v>3.106006593204905</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08880088812809435</v>
+        <v>0.08868221997346615</v>
       </c>
       <c r="C41">
-        <v>342.5384742679621</v>
+        <v>338.8684469047498</v>
       </c>
       <c r="D41">
-        <v>516.738474267962</v>
+        <v>518.1684469047498</v>
       </c>
       <c r="E41">
-        <v>135.1</v>
+        <v>140.2</v>
       </c>
       <c r="F41">
-        <v>198.9</v>
+        <v>204</v>
       </c>
       <c r="G41">
         <v>24.7</v>
@@ -4649,28 +4649,28 @@
         <v>39.6</v>
       </c>
       <c r="M41">
-        <v>12.74949</v>
+        <v>13.0764</v>
       </c>
       <c r="N41">
-        <v>26.85051</v>
+        <v>26.5236</v>
       </c>
       <c r="O41">
-        <v>7.2496377</v>
+        <v>7.161372000000001</v>
       </c>
       <c r="P41">
-        <v>19.6008723</v>
+        <v>19.362228</v>
       </c>
       <c r="Q41">
-        <v>27.30087229999999</v>
+        <v>27.062228</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1156583903739252</v>
+        <v>0.1166083666224436</v>
       </c>
       <c r="T41">
-        <v>1.279480952951791</v>
+        <v>1.296880101561284</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.106006593204905</v>
+        <v>3.028356428374782</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08868221997346615</v>
+        <v>0.09089809181883794</v>
       </c>
       <c r="C42">
-        <v>338.8684469047498</v>
+        <v>308.3085033384313</v>
       </c>
       <c r="D42">
-        <v>518.1684469047498</v>
+        <v>492.7085033384313</v>
       </c>
       <c r="E42">
-        <v>140.2</v>
+        <v>145.3</v>
       </c>
       <c r="F42">
-        <v>204</v>
+        <v>209.1</v>
       </c>
       <c r="G42">
         <v>24.7</v>
@@ -4731,45 +4731,45 @@
         <v>39.6</v>
       </c>
       <c r="M42">
-        <v>13.0764</v>
+        <v>15.03429</v>
       </c>
       <c r="N42">
-        <v>26.5236</v>
+        <v>24.56571</v>
       </c>
       <c r="O42">
-        <v>7.161372000000001</v>
+        <v>6.6327417</v>
       </c>
       <c r="P42">
-        <v>19.362228</v>
+        <v>17.9329683</v>
       </c>
       <c r="Q42">
-        <v>27.062228</v>
+        <v>25.63296829999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1166083666224436</v>
+        <v>0.1175905454556575</v>
       </c>
       <c r="T42">
-        <v>1.296880101561284</v>
+        <v>1.314869051818556</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.028356428374782</v>
+        <v>2.633978724635483</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09089809181883794</v>
+        <v>0.09083636366420973</v>
       </c>
       <c r="C43">
-        <v>308.3085033384313</v>
+        <v>303.8838239950339</v>
       </c>
       <c r="D43">
-        <v>492.7085033384313</v>
+        <v>493.383823995034</v>
       </c>
       <c r="E43">
-        <v>145.3</v>
+        <v>150.4</v>
       </c>
       <c r="F43">
-        <v>209.1</v>
+        <v>214.2</v>
       </c>
       <c r="G43">
         <v>24.7</v>
@@ -4813,28 +4813,28 @@
         <v>39.6</v>
       </c>
       <c r="M43">
-        <v>15.03429</v>
+        <v>15.40098</v>
       </c>
       <c r="N43">
-        <v>24.56571</v>
+        <v>24.19902</v>
       </c>
       <c r="O43">
-        <v>6.6327417</v>
+        <v>6.533735399999999</v>
       </c>
       <c r="P43">
-        <v>17.9329683</v>
+        <v>17.6652846</v>
       </c>
       <c r="Q43">
-        <v>25.63296829999999</v>
+        <v>25.3652846</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1175905454556575</v>
+        <v>0.1186065925244995</v>
       </c>
       <c r="T43">
-        <v>1.314869051818556</v>
+        <v>1.33347831070539</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.633978724635483</v>
+        <v>2.571264945477495</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09083636366420975</v>
+        <v>0.09077463550958152</v>
       </c>
       <c r="C44">
-        <v>303.8838239950338</v>
+        <v>299.4609984208753</v>
       </c>
       <c r="D44">
-        <v>493.3838239950338</v>
+        <v>494.0609984208753</v>
       </c>
       <c r="E44">
-        <v>150.4</v>
+        <v>155.5</v>
       </c>
       <c r="F44">
-        <v>214.2</v>
+        <v>219.3</v>
       </c>
       <c r="G44">
         <v>24.7</v>
@@ -4895,28 +4895,28 @@
         <v>39.6</v>
       </c>
       <c r="M44">
-        <v>15.40098</v>
+        <v>15.76767</v>
       </c>
       <c r="N44">
-        <v>24.19902</v>
+        <v>23.83233</v>
       </c>
       <c r="O44">
-        <v>6.5337354</v>
+        <v>6.4347291</v>
       </c>
       <c r="P44">
-        <v>17.6652846</v>
+        <v>17.3976009</v>
       </c>
       <c r="Q44">
-        <v>25.3652846</v>
+        <v>25.0976009</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1186065925244995</v>
+        <v>0.1196582903676869</v>
       </c>
       <c r="T44">
-        <v>1.33347831070539</v>
+        <v>1.352740526044393</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.571264945477496</v>
+        <v>2.511468086280344</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09077463550958152</v>
+        <v>0.09196558735495333</v>
       </c>
       <c r="C45">
-        <v>299.4609984208753</v>
+        <v>281.6155121938393</v>
       </c>
       <c r="D45">
-        <v>494.0609984208753</v>
+        <v>481.3155121938394</v>
       </c>
       <c r="E45">
-        <v>155.5</v>
+        <v>160.6</v>
       </c>
       <c r="F45">
-        <v>219.3</v>
+        <v>224.4</v>
       </c>
       <c r="G45">
         <v>24.7</v>
@@ -4977,45 +4977,45 @@
         <v>39.6</v>
       </c>
       <c r="M45">
-        <v>15.76767</v>
+        <v>17.00952</v>
       </c>
       <c r="N45">
-        <v>23.83233</v>
+        <v>22.59048</v>
       </c>
       <c r="O45">
-        <v>6.4347291</v>
+        <v>6.099429600000001</v>
       </c>
       <c r="P45">
-        <v>17.3976009</v>
+        <v>16.4910504</v>
       </c>
       <c r="Q45">
-        <v>25.0976009</v>
+        <v>24.19105039999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1196582903676869</v>
+        <v>0.1207475488481309</v>
       </c>
       <c r="T45">
-        <v>1.352740526044393</v>
+        <v>1.372690677645504</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.511468086280344</v>
+        <v>2.328108024212323</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09196558735495333</v>
+        <v>0.09193232920032511</v>
       </c>
       <c r="C46">
-        <v>281.6155121938393</v>
+        <v>276.8625067203891</v>
       </c>
       <c r="D46">
-        <v>481.3155121938394</v>
+        <v>481.6625067203891</v>
       </c>
       <c r="E46">
-        <v>160.6</v>
+        <v>165.7</v>
       </c>
       <c r="F46">
-        <v>224.4</v>
+        <v>229.5</v>
       </c>
       <c r="G46">
         <v>24.7</v>
@@ -5059,28 +5059,28 @@
         <v>39.6</v>
       </c>
       <c r="M46">
-        <v>17.00952</v>
+        <v>17.3961</v>
       </c>
       <c r="N46">
-        <v>22.59048</v>
+        <v>22.2039</v>
       </c>
       <c r="O46">
-        <v>6.099429600000001</v>
+        <v>5.995053</v>
       </c>
       <c r="P46">
-        <v>16.4910504</v>
+        <v>16.208847</v>
       </c>
       <c r="Q46">
-        <v>24.19105039999999</v>
+        <v>23.90884699999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1207475488481309</v>
+        <v>0.1218764167278638</v>
       </c>
       <c r="T46">
-        <v>1.372690677645504</v>
+        <v>1.393366289304836</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.328108024212323</v>
+        <v>2.276372290340938</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09193232920032511</v>
+        <v>0.09189907104569692</v>
       </c>
       <c r="C47">
-        <v>276.8625067203891</v>
+        <v>272.1100019250372</v>
       </c>
       <c r="D47">
-        <v>481.6625067203891</v>
+        <v>482.0100019250372</v>
       </c>
       <c r="E47">
-        <v>165.7</v>
+        <v>170.8</v>
       </c>
       <c r="F47">
-        <v>229.5</v>
+        <v>234.6</v>
       </c>
       <c r="G47">
         <v>24.7</v>
@@ -5141,28 +5141,28 @@
         <v>39.6</v>
       </c>
       <c r="M47">
-        <v>17.3961</v>
+        <v>17.78268</v>
       </c>
       <c r="N47">
-        <v>22.2039</v>
+        <v>21.81732</v>
       </c>
       <c r="O47">
-        <v>5.995053</v>
+        <v>5.8906764</v>
       </c>
       <c r="P47">
-        <v>16.208847</v>
+        <v>15.9266436</v>
       </c>
       <c r="Q47">
-        <v>23.90884699999999</v>
+        <v>23.62664359999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1218764167278638</v>
+        <v>0.1230470945290684</v>
       </c>
       <c r="T47">
-        <v>1.393366289304836</v>
+        <v>1.414807664358959</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.276372290340938</v>
+        <v>2.226885936203092</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09189907104569692</v>
+        <v>0.09186581289106871</v>
       </c>
       <c r="C48">
-        <v>272.1100019250372</v>
+        <v>267.3579988922083</v>
       </c>
       <c r="D48">
-        <v>482.0100019250372</v>
+        <v>482.3579988922083</v>
       </c>
       <c r="E48">
-        <v>170.8</v>
+        <v>175.9</v>
       </c>
       <c r="F48">
-        <v>234.6</v>
+        <v>239.7</v>
       </c>
       <c r="G48">
         <v>24.7</v>
@@ -5223,28 +5223,28 @@
         <v>39.6</v>
       </c>
       <c r="M48">
-        <v>17.78268</v>
+        <v>18.16926</v>
       </c>
       <c r="N48">
-        <v>21.81732</v>
+        <v>21.43074</v>
       </c>
       <c r="O48">
-        <v>5.8906764</v>
+        <v>5.7862998</v>
       </c>
       <c r="P48">
-        <v>15.9266436</v>
+        <v>15.6444402</v>
       </c>
       <c r="Q48">
-        <v>23.62664359999999</v>
+        <v>23.34444019999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1230470945290684</v>
+        <v>0.124261948851073</v>
       </c>
       <c r="T48">
-        <v>1.414807664358959</v>
+        <v>1.43705814790569</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.226885936203092</v>
+        <v>2.179505384368984</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09186581289106871</v>
+        <v>0.0918325547364405</v>
       </c>
       <c r="C49">
-        <v>267.3579988922083</v>
+        <v>262.6064987094607</v>
       </c>
       <c r="D49">
-        <v>482.3579988922083</v>
+        <v>482.7064987094607</v>
       </c>
       <c r="E49">
-        <v>175.9</v>
+        <v>181</v>
       </c>
       <c r="F49">
-        <v>239.7</v>
+        <v>244.8</v>
       </c>
       <c r="G49">
         <v>24.7</v>
@@ -5305,28 +5305,28 @@
         <v>39.6</v>
       </c>
       <c r="M49">
-        <v>18.16926</v>
+        <v>18.55584</v>
       </c>
       <c r="N49">
-        <v>21.43074</v>
+        <v>21.04416</v>
       </c>
       <c r="O49">
-        <v>5.7862998</v>
+        <v>5.6819232</v>
       </c>
       <c r="P49">
-        <v>15.6444402</v>
+        <v>15.3622368</v>
       </c>
       <c r="Q49">
-        <v>23.34444019999999</v>
+        <v>23.06223679999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.124261948851073</v>
+        <v>0.1255235283393087</v>
       </c>
       <c r="T49">
-        <v>1.43705814790569</v>
+        <v>1.460164419281142</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.179505384368984</v>
+        <v>2.134099022194629</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0918325547364405</v>
+        <v>0.0917992965818123</v>
       </c>
       <c r="C50">
-        <v>262.6064987094607</v>
+        <v>257.8555024674979</v>
       </c>
       <c r="D50">
-        <v>482.7064987094607</v>
+        <v>483.0555024674979</v>
       </c>
       <c r="E50">
-        <v>181</v>
+        <v>186.1</v>
       </c>
       <c r="F50">
-        <v>244.8</v>
+        <v>249.9</v>
       </c>
       <c r="G50">
         <v>24.7</v>
@@ -5387,28 +5387,28 @@
         <v>39.6</v>
       </c>
       <c r="M50">
-        <v>18.55584</v>
+        <v>18.94242</v>
       </c>
       <c r="N50">
-        <v>21.04416</v>
+        <v>20.65758</v>
       </c>
       <c r="O50">
-        <v>5.681923200000001</v>
+        <v>5.5775466</v>
       </c>
       <c r="P50">
-        <v>15.3622368</v>
+        <v>15.0800334</v>
       </c>
       <c r="Q50">
-        <v>23.0622368</v>
+        <v>22.78003339999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1255235283393087</v>
+        <v>0.1268345815329653</v>
       </c>
       <c r="T50">
-        <v>1.460164419281142</v>
+        <v>1.484176818945827</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.13409902219463</v>
+        <v>2.090545980925351</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0917992965818123</v>
+        <v>0.09176603842718409</v>
       </c>
       <c r="C51">
-        <v>257.8555024674979</v>
+        <v>253.1050112601802</v>
       </c>
       <c r="D51">
-        <v>483.0555024674979</v>
+        <v>483.4050112601802</v>
       </c>
       <c r="E51">
-        <v>186.1</v>
+        <v>191.2</v>
       </c>
       <c r="F51">
-        <v>249.9</v>
+        <v>255</v>
       </c>
       <c r="G51">
         <v>24.7</v>
@@ -5469,28 +5469,28 @@
         <v>39.6</v>
       </c>
       <c r="M51">
-        <v>18.94242</v>
+        <v>19.329</v>
       </c>
       <c r="N51">
-        <v>20.65758</v>
+        <v>20.271</v>
       </c>
       <c r="O51">
-        <v>5.5775466</v>
+        <v>5.473170000000001</v>
       </c>
       <c r="P51">
-        <v>15.0800334</v>
+        <v>14.79783</v>
       </c>
       <c r="Q51">
-        <v>22.78003339999999</v>
+        <v>22.49783</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1268345815329653</v>
+        <v>0.1281980768543682</v>
       </c>
       <c r="T51">
-        <v>1.484176818945827</v>
+        <v>1.5091497145971</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.090545980925351</v>
+        <v>2.048735061306845</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09176603842718409</v>
+        <v>0.09173278027255588</v>
       </c>
       <c r="C52">
-        <v>253.1050112601802</v>
+        <v>248.3550261845357</v>
       </c>
       <c r="D52">
-        <v>483.4050112601802</v>
+        <v>483.7550261845358</v>
       </c>
       <c r="E52">
-        <v>191.2</v>
+        <v>196.3</v>
       </c>
       <c r="F52">
-        <v>255</v>
+        <v>260.1</v>
       </c>
       <c r="G52">
         <v>24.7</v>
@@ -5551,28 +5551,28 @@
         <v>39.6</v>
       </c>
       <c r="M52">
-        <v>19.329</v>
+        <v>19.71558</v>
       </c>
       <c r="N52">
-        <v>20.271</v>
+        <v>19.88442</v>
       </c>
       <c r="O52">
-        <v>5.473170000000001</v>
+        <v>5.3687934</v>
       </c>
       <c r="P52">
-        <v>14.79783</v>
+        <v>14.5156266</v>
       </c>
       <c r="Q52">
-        <v>22.49783</v>
+        <v>22.21562659999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1281980768543682</v>
+        <v>0.1296172250460324</v>
       </c>
       <c r="T52">
-        <v>1.5091497145971</v>
+        <v>1.535141912111689</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.048735061306845</v>
+        <v>2.008563785594945</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09173278027255588</v>
+        <v>0.09708984211792769</v>
       </c>
       <c r="C53">
-        <v>248.3550261845357</v>
+        <v>192.7283431949191</v>
       </c>
       <c r="D53">
-        <v>483.7550261845358</v>
+        <v>433.2283431949191</v>
       </c>
       <c r="E53">
-        <v>196.3</v>
+        <v>201.4</v>
       </c>
       <c r="F53">
-        <v>260.1</v>
+        <v>265.2</v>
       </c>
       <c r="G53">
         <v>24.7</v>
@@ -5633,45 +5633,45 @@
         <v>39.6</v>
       </c>
       <c r="M53">
-        <v>19.71558</v>
+        <v>23.868</v>
       </c>
       <c r="N53">
-        <v>19.88442</v>
+        <v>15.732</v>
       </c>
       <c r="O53">
-        <v>5.3687934</v>
+        <v>4.247640000000001</v>
       </c>
       <c r="P53">
-        <v>14.5156266</v>
+        <v>11.48436</v>
       </c>
       <c r="Q53">
-        <v>22.21562659999999</v>
+        <v>19.18436</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1296172250460324</v>
+        <v>0.1310955044123494</v>
       </c>
       <c r="T53">
-        <v>1.535141912111689</v>
+        <v>1.562217117856054</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.008563785594945</v>
+        <v>1.659125188536954</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09708984211792769</v>
+        <v>0.09716024396329948</v>
       </c>
       <c r="C54">
-        <v>192.7283431949191</v>
+        <v>187.0344972067638</v>
       </c>
       <c r="D54">
-        <v>433.2283431949191</v>
+        <v>432.6344972067639</v>
       </c>
       <c r="E54">
-        <v>201.4</v>
+        <v>206.5</v>
       </c>
       <c r="F54">
-        <v>265.2</v>
+        <v>270.3</v>
       </c>
       <c r="G54">
         <v>24.7</v>
@@ -5715,28 +5715,28 @@
         <v>39.6</v>
       </c>
       <c r="M54">
-        <v>23.868</v>
+        <v>24.327</v>
       </c>
       <c r="N54">
-        <v>15.732</v>
+        <v>15.273</v>
       </c>
       <c r="O54">
-        <v>4.247640000000001</v>
+        <v>4.12371</v>
       </c>
       <c r="P54">
-        <v>11.48436</v>
+        <v>11.14929</v>
       </c>
       <c r="Q54">
-        <v>19.18436</v>
+        <v>18.84929</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1310955044123494</v>
+        <v>0.1326366892836159</v>
       </c>
       <c r="T54">
-        <v>1.562217117856054</v>
+        <v>1.590444460015072</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.659125188536954</v>
+        <v>1.627820939696633</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09716024396329948</v>
+        <v>0.09723064580867127</v>
       </c>
       <c r="C55">
-        <v>187.0344972067638</v>
+        <v>181.3422770139985</v>
       </c>
       <c r="D55">
-        <v>432.6344972067639</v>
+        <v>432.0422770139986</v>
       </c>
       <c r="E55">
-        <v>206.5</v>
+        <v>211.6</v>
       </c>
       <c r="F55">
-        <v>270.3</v>
+        <v>275.4</v>
       </c>
       <c r="G55">
         <v>24.7</v>
@@ -5797,28 +5797,28 @@
         <v>39.6</v>
       </c>
       <c r="M55">
-        <v>24.327</v>
+        <v>24.786</v>
       </c>
       <c r="N55">
-        <v>15.273</v>
+        <v>14.814</v>
       </c>
       <c r="O55">
-        <v>4.12371</v>
+        <v>3.99978</v>
       </c>
       <c r="P55">
-        <v>11.14929</v>
+        <v>10.81422</v>
       </c>
       <c r="Q55">
-        <v>18.84929</v>
+        <v>18.51421999999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1326366892836159</v>
+        <v>0.1342448821927636</v>
       </c>
       <c r="T55">
-        <v>1.590444460015072</v>
+        <v>1.619899077920134</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.627820939696633</v>
+        <v>1.597676107480029</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09723064580867127</v>
+        <v>0.09730104765404307</v>
       </c>
       <c r="C56">
-        <v>181.3422770139985</v>
+        <v>175.6516759492446</v>
       </c>
       <c r="D56">
-        <v>432.0422770139986</v>
+        <v>431.4516759492446</v>
       </c>
       <c r="E56">
-        <v>211.6</v>
+        <v>216.7</v>
       </c>
       <c r="F56">
-        <v>275.4</v>
+        <v>280.5</v>
       </c>
       <c r="G56">
         <v>24.7</v>
@@ -5879,28 +5879,28 @@
         <v>39.6</v>
       </c>
       <c r="M56">
-        <v>24.786</v>
+        <v>25.245</v>
       </c>
       <c r="N56">
-        <v>14.814</v>
+        <v>14.355</v>
       </c>
       <c r="O56">
-        <v>3.99978</v>
+        <v>3.875850000000001</v>
       </c>
       <c r="P56">
-        <v>10.81422</v>
+        <v>10.47915</v>
       </c>
       <c r="Q56">
-        <v>18.51421999999999</v>
+        <v>18.17915</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1342448821927636</v>
+        <v>0.135924550342318</v>
       </c>
       <c r="T56">
-        <v>1.619899077920134</v>
+        <v>1.65066278995431</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.597676107480029</v>
+        <v>1.568627450980392</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09730104765404307</v>
+        <v>0.09737144949941487</v>
       </c>
       <c r="C57">
-        <v>175.6516759492446</v>
+        <v>169.9626873815308</v>
       </c>
       <c r="D57">
-        <v>431.4516759492446</v>
+        <v>430.8626873815309</v>
       </c>
       <c r="E57">
-        <v>216.7</v>
+        <v>221.8</v>
       </c>
       <c r="F57">
-        <v>280.5</v>
+        <v>285.6</v>
       </c>
       <c r="G57">
         <v>24.7</v>
@@ -5961,28 +5961,28 @@
         <v>39.6</v>
       </c>
       <c r="M57">
-        <v>25.245</v>
+        <v>25.704</v>
       </c>
       <c r="N57">
-        <v>14.355</v>
+        <v>13.896</v>
       </c>
       <c r="O57">
-        <v>3.875850000000001</v>
+        <v>3.751920000000001</v>
       </c>
       <c r="P57">
-        <v>10.47915</v>
+        <v>10.14408</v>
       </c>
       <c r="Q57">
-        <v>18.17915</v>
+        <v>17.84408</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.135924550342318</v>
+        <v>0.1376805670441247</v>
       </c>
       <c r="T57">
-        <v>1.65066278995431</v>
+        <v>1.682824852535494</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.568627450980392</v>
+        <v>1.540616246498599</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09737144949941487</v>
+        <v>0.09744185134478667</v>
       </c>
       <c r="C58">
-        <v>169.9626873815308</v>
+        <v>164.2753047160452</v>
       </c>
       <c r="D58">
-        <v>430.8626873815309</v>
+        <v>430.2753047160453</v>
       </c>
       <c r="E58">
-        <v>221.8</v>
+        <v>226.9</v>
       </c>
       <c r="F58">
-        <v>285.6</v>
+        <v>290.7</v>
       </c>
       <c r="G58">
         <v>24.7</v>
@@ -6043,28 +6043,28 @@
         <v>39.6</v>
       </c>
       <c r="M58">
-        <v>25.704</v>
+        <v>26.163</v>
       </c>
       <c r="N58">
-        <v>13.896</v>
+        <v>13.437</v>
       </c>
       <c r="O58">
-        <v>3.751920000000001</v>
+        <v>3.62799</v>
       </c>
       <c r="P58">
-        <v>10.14408</v>
+        <v>9.809009999999997</v>
       </c>
       <c r="Q58">
-        <v>17.84408</v>
+        <v>17.50900999999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1376805670441247</v>
+        <v>0.1395182589413644</v>
       </c>
       <c r="T58">
-        <v>1.682824852535494</v>
+        <v>1.716482825004175</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.540616246498599</v>
+        <v>1.513587891296869</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09744185134478667</v>
+        <v>0.1242422862728262</v>
       </c>
       <c r="C59">
-        <v>164.2753047160452</v>
+        <v>12.1683030960595</v>
       </c>
       <c r="D59">
-        <v>430.2753047160453</v>
+        <v>283.2683030960595</v>
       </c>
       <c r="E59">
-        <v>226.9</v>
+        <v>232</v>
       </c>
       <c r="F59">
-        <v>290.7</v>
+        <v>295.8</v>
       </c>
       <c r="G59">
         <v>24.7</v>
@@ -6125,45 +6125,45 @@
         <v>39.6</v>
       </c>
       <c r="M59">
-        <v>26.163</v>
+        <v>43.42344000000001</v>
       </c>
       <c r="N59">
-        <v>13.437</v>
+        <v>-3.823440000000005</v>
       </c>
       <c r="O59">
-        <v>3.62799</v>
+        <v>-1.032328800000001</v>
       </c>
       <c r="P59">
-        <v>9.809009999999997</v>
+        <v>-2.791111200000004</v>
       </c>
       <c r="Q59">
-        <v>17.50900999999999</v>
+        <v>4.908888799999993</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1395182589413644</v>
+        <v>0.1430071241789979</v>
       </c>
       <c r="T59">
-        <v>1.716482825004175</v>
+        <v>1.780382617070297</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.27</v>
+        <v>0.2462264620214336</v>
       </c>
       <c r="W59">
-        <v>0.06569999999999999</v>
+        <v>0.1106539553752536</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.513587891296869</v>
+        <v>0.9119498593386428</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1242422862728262</v>
+        <v>0.1252522862728262</v>
       </c>
       <c r="C60">
-        <v>12.16830309605962</v>
+        <v>3.46738738238713</v>
       </c>
       <c r="D60">
-        <v>283.2683030960596</v>
+        <v>279.6673873823871</v>
       </c>
       <c r="E60">
-        <v>231.9999999999999</v>
+        <v>237.1</v>
       </c>
       <c r="F60">
-        <v>295.8</v>
+        <v>300.9</v>
       </c>
       <c r="G60">
         <v>24.7</v>
@@ -6207,37 +6207,37 @@
         <v>39.6</v>
       </c>
       <c r="M60">
-        <v>43.42344</v>
+        <v>44.17212</v>
       </c>
       <c r="N60">
-        <v>-3.823439999999998</v>
+        <v>-4.572119999999998</v>
       </c>
       <c r="O60">
-        <v>-1.032328799999999</v>
+        <v>-1.2344724</v>
       </c>
       <c r="P60">
-        <v>-2.791111199999999</v>
+        <v>-3.337647599999999</v>
       </c>
       <c r="Q60">
-        <v>4.908888799999997</v>
+        <v>4.362352399999997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1430071241789979</v>
+        <v>0.1453780296467783</v>
       </c>
       <c r="T60">
-        <v>1.780382617070296</v>
+        <v>1.823806583340304</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2462264620214336</v>
+        <v>0.2420531321566636</v>
       </c>
       <c r="W60">
-        <v>0.1106539553752536</v>
+        <v>0.1112666001994018</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9119498593386429</v>
+        <v>0.8964930820617167</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1252522862728262</v>
+        <v>0.1262622862728262</v>
       </c>
       <c r="C61">
-        <v>3.46738738238713</v>
+        <v>-5.143127597245098</v>
       </c>
       <c r="D61">
-        <v>279.6673873823871</v>
+        <v>276.1568724027549</v>
       </c>
       <c r="E61">
-        <v>237.1</v>
+        <v>242.2</v>
       </c>
       <c r="F61">
-        <v>300.9</v>
+        <v>306</v>
       </c>
       <c r="G61">
         <v>24.7</v>
@@ -6289,37 +6289,37 @@
         <v>39.6</v>
       </c>
       <c r="M61">
-        <v>44.17212</v>
+        <v>44.92080000000001</v>
       </c>
       <c r="N61">
-        <v>-4.572119999999998</v>
+        <v>-5.320800000000006</v>
       </c>
       <c r="O61">
-        <v>-1.2344724</v>
+        <v>-1.436616000000002</v>
       </c>
       <c r="P61">
-        <v>-3.337647599999999</v>
+        <v>-3.884184000000004</v>
       </c>
       <c r="Q61">
-        <v>4.362352399999997</v>
+        <v>3.815815999999992</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1453780296467783</v>
+        <v>0.1478674803879478</v>
       </c>
       <c r="T61">
-        <v>1.823806583340304</v>
+        <v>1.869401747923811</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2420531321566636</v>
+        <v>0.2380189132873858</v>
       </c>
       <c r="W61">
-        <v>0.1112666001994018</v>
+        <v>0.1118588235294118</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8964930820617167</v>
+        <v>0.8815515306940214</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1262622862728262</v>
+        <v>0.1272722862728262</v>
       </c>
       <c r="C62">
-        <v>-5.143127597245098</v>
+        <v>-13.66660389681482</v>
       </c>
       <c r="D62">
-        <v>276.1568724027549</v>
+        <v>272.7333961031852</v>
       </c>
       <c r="E62">
-        <v>242.2</v>
+        <v>247.3</v>
       </c>
       <c r="F62">
-        <v>306</v>
+        <v>311.1</v>
       </c>
       <c r="G62">
         <v>24.7</v>
@@ -6371,37 +6371,37 @@
         <v>39.6</v>
       </c>
       <c r="M62">
-        <v>44.92080000000001</v>
+        <v>45.66948</v>
       </c>
       <c r="N62">
-        <v>-5.320800000000006</v>
+        <v>-6.069479999999999</v>
       </c>
       <c r="O62">
-        <v>-1.436616000000002</v>
+        <v>-1.6387596</v>
       </c>
       <c r="P62">
-        <v>-3.884184000000004</v>
+        <v>-4.430720399999998</v>
       </c>
       <c r="Q62">
-        <v>3.815815999999992</v>
+        <v>3.269279599999997</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1478674803879478</v>
+        <v>0.15048459526969</v>
       </c>
       <c r="T62">
-        <v>1.869401747923811</v>
+        <v>1.917335126075704</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2380189132873858</v>
+        <v>0.2341169638892319</v>
       </c>
       <c r="W62">
-        <v>0.1118588235294118</v>
+        <v>0.1124316297010608</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8815515306940214</v>
+        <v>0.8670998662564147</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1272722862728262</v>
+        <v>0.1282822862728262</v>
       </c>
       <c r="C63">
-        <v>-13.66660389681482</v>
+        <v>-22.10623889617796</v>
       </c>
       <c r="D63">
-        <v>272.7333961031852</v>
+        <v>269.393761103822</v>
       </c>
       <c r="E63">
-        <v>247.3</v>
+        <v>252.4</v>
       </c>
       <c r="F63">
-        <v>311.1</v>
+        <v>316.2</v>
       </c>
       <c r="G63">
         <v>24.7</v>
@@ -6453,37 +6453,37 @@
         <v>39.6</v>
       </c>
       <c r="M63">
-        <v>45.66948</v>
+        <v>46.41816</v>
       </c>
       <c r="N63">
-        <v>-6.069479999999999</v>
+        <v>-6.818159999999999</v>
       </c>
       <c r="O63">
-        <v>-1.6387596</v>
+        <v>-1.8409032</v>
       </c>
       <c r="P63">
-        <v>-4.430720399999998</v>
+        <v>-4.977256799999999</v>
       </c>
       <c r="Q63">
-        <v>3.269279599999997</v>
+        <v>2.722743199999996</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.15048459526969</v>
+        <v>0.153239453039945</v>
       </c>
       <c r="T63">
-        <v>1.917335126075704</v>
+        <v>1.967791313604012</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2341169638892319</v>
+        <v>0.2303408838265024</v>
       </c>
       <c r="W63">
-        <v>0.1124316297010608</v>
+        <v>0.1129859582542695</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8670998662564147</v>
+        <v>0.8531143845426015</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1282822862728262</v>
+        <v>0.1292922862728262</v>
       </c>
       <c r="C64">
-        <v>-22.10623889617796</v>
+        <v>-30.46507526132154</v>
       </c>
       <c r="D64">
-        <v>269.393761103822</v>
+        <v>266.1349247386785</v>
       </c>
       <c r="E64">
-        <v>252.4</v>
+        <v>257.5</v>
       </c>
       <c r="F64">
-        <v>316.2</v>
+        <v>321.3</v>
       </c>
       <c r="G64">
         <v>24.7</v>
@@ -6535,37 +6535,37 @@
         <v>39.6</v>
       </c>
       <c r="M64">
-        <v>46.41816</v>
+        <v>47.16684000000001</v>
       </c>
       <c r="N64">
-        <v>-6.818159999999999</v>
+        <v>-7.566840000000006</v>
       </c>
       <c r="O64">
-        <v>-1.8409032</v>
+        <v>-2.043046800000002</v>
       </c>
       <c r="P64">
-        <v>-4.977256799999999</v>
+        <v>-5.523793200000005</v>
       </c>
       <c r="Q64">
-        <v>2.722743199999996</v>
+        <v>2.176206799999991</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.153239453039945</v>
+        <v>0.1561432220410246</v>
       </c>
       <c r="T64">
-        <v>1.967791313604012</v>
+        <v>2.020974862620336</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2303408838265024</v>
+        <v>0.2266846793213198</v>
       </c>
       <c r="W64">
-        <v>0.1129859582542695</v>
+        <v>0.1135226890756303</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8531143845426015</v>
+        <v>0.8395728863752585</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1292922862728262</v>
+        <v>0.1303022862728262</v>
       </c>
       <c r="C65">
-        <v>-30.46507526132154</v>
+        <v>-38.74601019032713</v>
       </c>
       <c r="D65">
-        <v>266.1349247386785</v>
+        <v>262.9539898096729</v>
       </c>
       <c r="E65">
-        <v>257.5</v>
+        <v>262.6</v>
       </c>
       <c r="F65">
-        <v>321.3</v>
+        <v>326.4</v>
       </c>
       <c r="G65">
         <v>24.7</v>
@@ -6617,37 +6617,37 @@
         <v>39.6</v>
       </c>
       <c r="M65">
-        <v>47.16684000000001</v>
+        <v>47.91552000000001</v>
       </c>
       <c r="N65">
-        <v>-7.566840000000006</v>
+        <v>-8.315520000000006</v>
       </c>
       <c r="O65">
-        <v>-2.043046800000002</v>
+        <v>-2.245190400000002</v>
       </c>
       <c r="P65">
-        <v>-5.523793200000005</v>
+        <v>-6.070329600000004</v>
       </c>
       <c r="Q65">
-        <v>2.176206799999991</v>
+        <v>1.629670399999991</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1561432220410246</v>
+        <v>0.1592083115421642</v>
       </c>
       <c r="T65">
-        <v>2.020974862620336</v>
+        <v>2.077113053248679</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2266846793213198</v>
+        <v>0.2231427312069242</v>
       </c>
       <c r="W65">
-        <v>0.1135226890756303</v>
+        <v>0.1140426470588235</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8395728863752585</v>
+        <v>0.826454560025645</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1303022862728262</v>
+        <v>0.1313122862728262</v>
       </c>
       <c r="C66">
-        <v>-38.74601019032713</v>
+        <v>-46.95180400410061</v>
       </c>
       <c r="D66">
-        <v>262.9539898096729</v>
+        <v>259.8481959958994</v>
       </c>
       <c r="E66">
-        <v>262.6</v>
+        <v>267.7</v>
       </c>
       <c r="F66">
-        <v>326.4</v>
+        <v>331.5</v>
       </c>
       <c r="G66">
         <v>24.7</v>
@@ -6699,37 +6699,37 @@
         <v>39.6</v>
       </c>
       <c r="M66">
-        <v>47.91552000000001</v>
+        <v>48.66420000000001</v>
       </c>
       <c r="N66">
-        <v>-8.315520000000006</v>
+        <v>-9.064200000000007</v>
       </c>
       <c r="O66">
-        <v>-2.245190400000002</v>
+        <v>-2.447334000000002</v>
       </c>
       <c r="P66">
-        <v>-6.070329600000004</v>
+        <v>-6.616866000000005</v>
       </c>
       <c r="Q66">
-        <v>1.629670399999991</v>
+        <v>1.08313399999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1592083115421642</v>
+        <v>0.1624485490147975</v>
       </c>
       <c r="T66">
-        <v>2.077113053248679</v>
+        <v>2.136459140484356</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2231427312069242</v>
+        <v>0.219709766111433</v>
       </c>
       <c r="W66">
-        <v>0.1140426470588235</v>
+        <v>0.1145466063348416</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.826454560025645</v>
+        <v>0.813739874486789</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1313122862728262</v>
+        <v>0.1323222862728262</v>
       </c>
       <c r="C67">
-        <v>-46.95180400410061</v>
+        <v>-55.08508813540874</v>
       </c>
       <c r="D67">
-        <v>259.8481959958994</v>
+        <v>256.8149118645913</v>
       </c>
       <c r="E67">
-        <v>267.7</v>
+        <v>272.8</v>
       </c>
       <c r="F67">
-        <v>331.5</v>
+        <v>336.6</v>
       </c>
       <c r="G67">
         <v>24.7</v>
@@ -6781,37 +6781,37 @@
         <v>39.6</v>
       </c>
       <c r="M67">
-        <v>48.66420000000001</v>
+        <v>49.41288000000001</v>
       </c>
       <c r="N67">
-        <v>-9.064200000000007</v>
+        <v>-9.812880000000007</v>
       </c>
       <c r="O67">
-        <v>-2.447334000000002</v>
+        <v>-2.649477600000002</v>
       </c>
       <c r="P67">
-        <v>-6.616866000000005</v>
+        <v>-7.163402400000004</v>
       </c>
       <c r="Q67">
-        <v>1.08313399999999</v>
+        <v>0.5365975999999915</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1624485490147975</v>
+        <v>0.1658793886917033</v>
       </c>
       <c r="T67">
-        <v>2.136459140484356</v>
+        <v>2.199296174028013</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.219709766111433</v>
+        <v>0.2163808302612598</v>
       </c>
       <c r="W67">
-        <v>0.1145466063348416</v>
+        <v>0.1150352941176471</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.813739874486789</v>
+        <v>0.8014104824491104</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1323222862728262</v>
+        <v>0.1713414970107964</v>
       </c>
       <c r="C68">
-        <v>-55.08508813540874</v>
+        <v>-140.0050313836239</v>
       </c>
       <c r="D68">
-        <v>256.8149118645913</v>
+        <v>176.9949686163762</v>
       </c>
       <c r="E68">
-        <v>272.8</v>
+        <v>277.9</v>
       </c>
       <c r="F68">
-        <v>336.6</v>
+        <v>341.7</v>
       </c>
       <c r="G68">
         <v>24.7</v>
@@ -6863,45 +6863,45 @@
         <v>39.6</v>
       </c>
       <c r="M68">
-        <v>49.41288000000001</v>
+        <v>68.61336000000001</v>
       </c>
       <c r="N68">
-        <v>-9.812880000000007</v>
+        <v>-29.01336000000001</v>
       </c>
       <c r="O68">
-        <v>-2.649477600000002</v>
+        <v>-7.833607200000004</v>
       </c>
       <c r="P68">
-        <v>-7.163402400000004</v>
+        <v>-21.17975280000001</v>
       </c>
       <c r="Q68">
-        <v>0.5365975999999915</v>
+        <v>-13.47975280000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1658793886917033</v>
+        <v>0.1750612208883313</v>
       </c>
       <c r="T68">
-        <v>2.199296174028013</v>
+        <v>2.367464655235535</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.2163808302612598</v>
+        <v>0.1558297101322541</v>
       </c>
       <c r="W68">
-        <v>0.1150352941176471</v>
+        <v>0.1695093942054434</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8014104824491104</v>
+        <v>0.577147074563904</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1713414970107964</v>
+        <v>0.1728914970107964</v>
       </c>
       <c r="C69">
-        <v>-140.0050313836239</v>
+        <v>-147.2636510222931</v>
       </c>
       <c r="D69">
-        <v>176.9949686163762</v>
+        <v>174.8363489777069</v>
       </c>
       <c r="E69">
-        <v>277.9</v>
+        <v>283</v>
       </c>
       <c r="F69">
-        <v>341.7</v>
+        <v>346.8</v>
       </c>
       <c r="G69">
         <v>24.7</v>
@@ -6945,37 +6945,37 @@
         <v>39.6</v>
       </c>
       <c r="M69">
-        <v>68.61336000000001</v>
+        <v>69.63744</v>
       </c>
       <c r="N69">
-        <v>-29.01336000000001</v>
+        <v>-30.03744</v>
       </c>
       <c r="O69">
-        <v>-7.833607200000004</v>
+        <v>-8.110108799999999</v>
       </c>
       <c r="P69">
-        <v>-21.17975280000001</v>
+        <v>-21.9273312</v>
       </c>
       <c r="Q69">
-        <v>-13.47975280000001</v>
+        <v>-14.2273312</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1750612208883313</v>
+        <v>0.1791006340410917</v>
       </c>
       <c r="T69">
-        <v>2.367464655235535</v>
+        <v>2.441447925711645</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1558297101322541</v>
+        <v>0.1535380967479563</v>
       </c>
       <c r="W69">
-        <v>0.1695093942054434</v>
+        <v>0.1699695501730104</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.577147074563904</v>
+        <v>0.5686596175850233</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1728914970107964</v>
+        <v>0.1744414970107964</v>
       </c>
       <c r="C70">
-        <v>-147.2636510222931</v>
+        <v>-154.4702522918096</v>
       </c>
       <c r="D70">
-        <v>174.8363489777069</v>
+        <v>172.7297477081904</v>
       </c>
       <c r="E70">
-        <v>283</v>
+        <v>288.1</v>
       </c>
       <c r="F70">
-        <v>346.8</v>
+        <v>351.9</v>
       </c>
       <c r="G70">
         <v>24.7</v>
@@ -7027,37 +7027,37 @@
         <v>39.6</v>
       </c>
       <c r="M70">
-        <v>69.63744</v>
+        <v>70.66152000000001</v>
       </c>
       <c r="N70">
-        <v>-30.03744</v>
+        <v>-31.06152000000001</v>
       </c>
       <c r="O70">
-        <v>-8.110108799999999</v>
+        <v>-8.386610400000002</v>
       </c>
       <c r="P70">
-        <v>-21.9273312</v>
+        <v>-22.67490960000001</v>
       </c>
       <c r="Q70">
-        <v>-14.2273312</v>
+        <v>-14.97490960000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1791006340410917</v>
+        <v>0.1834006544940301</v>
       </c>
       <c r="T70">
-        <v>2.441447925711645</v>
+        <v>2.520204310412021</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1535380967479563</v>
+        <v>0.1513129069400149</v>
       </c>
       <c r="W70">
-        <v>0.1699695501730104</v>
+        <v>0.170416368286445</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5686596175850233</v>
+        <v>0.560418173851907</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1744414970107964</v>
+        <v>0.1759914970107964</v>
       </c>
       <c r="C71">
-        <v>-154.4702522918096</v>
+        <v>-161.6266931124071</v>
       </c>
       <c r="D71">
-        <v>172.7297477081904</v>
+        <v>170.673306887593</v>
       </c>
       <c r="E71">
-        <v>288.1</v>
+        <v>293.2</v>
       </c>
       <c r="F71">
-        <v>351.9</v>
+        <v>357.0000000000001</v>
       </c>
       <c r="G71">
         <v>24.7</v>
@@ -7109,37 +7109,37 @@
         <v>39.6</v>
       </c>
       <c r="M71">
-        <v>70.66152000000001</v>
+        <v>71.68560000000001</v>
       </c>
       <c r="N71">
-        <v>-31.06152000000001</v>
+        <v>-32.08560000000001</v>
       </c>
       <c r="O71">
-        <v>-8.386610400000002</v>
+        <v>-8.663112000000002</v>
       </c>
       <c r="P71">
-        <v>-22.67490960000001</v>
+        <v>-23.422488</v>
       </c>
       <c r="Q71">
-        <v>-14.97490960000001</v>
+        <v>-15.72248800000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1834006544940301</v>
+        <v>0.1879873429771645</v>
       </c>
       <c r="T71">
-        <v>2.520204310412021</v>
+        <v>2.604211120759088</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1513129069400149</v>
+        <v>0.1491512939837289</v>
       </c>
       <c r="W71">
-        <v>0.170416368286445</v>
+        <v>0.1708504201680672</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.560418173851907</v>
+        <v>0.5524121999397369</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1759914970107964</v>
+        <v>0.1775414970107964</v>
       </c>
       <c r="C72">
-        <v>-161.6266931124071</v>
+        <v>-168.7347439671358</v>
       </c>
       <c r="D72">
-        <v>170.673306887593</v>
+        <v>168.6652560328642</v>
       </c>
       <c r="E72">
-        <v>293.2</v>
+        <v>298.3</v>
       </c>
       <c r="F72">
-        <v>357.0000000000001</v>
+        <v>362.1</v>
       </c>
       <c r="G72">
         <v>24.7</v>
@@ -7191,37 +7191,37 @@
         <v>39.6</v>
       </c>
       <c r="M72">
-        <v>71.68560000000001</v>
+        <v>72.70968000000001</v>
       </c>
       <c r="N72">
-        <v>-32.08560000000001</v>
+        <v>-33.10968</v>
       </c>
       <c r="O72">
-        <v>-8.663112000000002</v>
+        <v>-8.939613600000001</v>
       </c>
       <c r="P72">
-        <v>-23.422488</v>
+        <v>-24.1700664</v>
       </c>
       <c r="Q72">
-        <v>-15.72248800000001</v>
+        <v>-16.47006640000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1879873429771645</v>
+        <v>0.1928903548039633</v>
       </c>
       <c r="T72">
-        <v>2.604211120759088</v>
+        <v>2.69401150423354</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1491512939837289</v>
+        <v>0.1470505715332539</v>
       </c>
       <c r="W72">
-        <v>0.1708504201680672</v>
+        <v>0.1712722452361226</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5524121999397369</v>
+        <v>0.5446317464194588</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1775414970107964</v>
+        <v>0.1790914970107964</v>
       </c>
       <c r="C73">
-        <v>-168.7347439671357</v>
+        <v>-175.7960929857439</v>
       </c>
       <c r="D73">
-        <v>168.6652560328643</v>
+        <v>166.7039070142561</v>
       </c>
       <c r="E73">
-        <v>298.3</v>
+        <v>303.4</v>
       </c>
       <c r="F73">
-        <v>362.1</v>
+        <v>367.2</v>
       </c>
       <c r="G73">
         <v>24.7</v>
@@ -7273,37 +7273,37 @@
         <v>39.6</v>
       </c>
       <c r="M73">
-        <v>72.70967999999999</v>
+        <v>73.73376</v>
       </c>
       <c r="N73">
-        <v>-33.10967999999999</v>
+        <v>-34.13376</v>
       </c>
       <c r="O73">
-        <v>-8.939613599999998</v>
+        <v>-9.216115200000001</v>
       </c>
       <c r="P73">
-        <v>-24.17006639999999</v>
+        <v>-24.9176448</v>
       </c>
       <c r="Q73">
-        <v>-16.4700664</v>
+        <v>-17.21764480000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1928903548039632</v>
+        <v>0.1981435817612476</v>
       </c>
       <c r="T73">
-        <v>2.694011504233539</v>
+        <v>2.790226200813308</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1470505715332539</v>
+        <v>0.1450082024841809</v>
       </c>
       <c r="W73">
-        <v>0.1712722452361226</v>
+        <v>0.1716823529411765</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.544631746419459</v>
+        <v>0.5370674166080776</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1790914970107964</v>
+        <v>0.1806414970107964</v>
       </c>
       <c r="C74">
-        <v>-175.7960929857439</v>
+        <v>-182.8123506779246</v>
       </c>
       <c r="D74">
-        <v>166.7039070142561</v>
+        <v>164.7876493220754</v>
       </c>
       <c r="E74">
-        <v>303.4</v>
+        <v>308.5</v>
       </c>
       <c r="F74">
-        <v>367.2</v>
+        <v>372.3</v>
       </c>
       <c r="G74">
         <v>24.7</v>
@@ -7355,37 +7355,37 @@
         <v>39.6</v>
       </c>
       <c r="M74">
-        <v>73.73376</v>
+        <v>74.75784</v>
       </c>
       <c r="N74">
-        <v>-34.13376</v>
+        <v>-35.15784</v>
       </c>
       <c r="O74">
-        <v>-9.216115200000001</v>
+        <v>-9.4926168</v>
       </c>
       <c r="P74">
-        <v>-24.9176448</v>
+        <v>-25.6652232</v>
       </c>
       <c r="Q74">
-        <v>-17.21764480000001</v>
+        <v>-17.9652232</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1981435817612476</v>
+        <v>0.2037859366412939</v>
       </c>
       <c r="T74">
-        <v>2.790226200813308</v>
+        <v>2.893567911954542</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1450082024841809</v>
+        <v>0.1430217887515209</v>
       </c>
       <c r="W74">
-        <v>0.1716823529411765</v>
+        <v>0.1720812248186946</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5370674166080776</v>
+        <v>0.5297103287093368</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1806414970107964</v>
+        <v>0.1821914970107964</v>
       </c>
       <c r="C75">
-        <v>-182.8123506779246</v>
+        <v>-189.785054343821</v>
       </c>
       <c r="D75">
-        <v>164.7876493220754</v>
+        <v>162.914945656179</v>
       </c>
       <c r="E75">
-        <v>308.5</v>
+        <v>313.6</v>
       </c>
       <c r="F75">
-        <v>372.3</v>
+        <v>377.4</v>
       </c>
       <c r="G75">
         <v>24.7</v>
@@ -7437,37 +7437,37 @@
         <v>39.6</v>
       </c>
       <c r="M75">
-        <v>74.75784</v>
+        <v>75.78192</v>
       </c>
       <c r="N75">
-        <v>-35.15784</v>
+        <v>-36.18192</v>
       </c>
       <c r="O75">
-        <v>-9.4926168</v>
+        <v>-9.7691184</v>
       </c>
       <c r="P75">
-        <v>-25.6652232</v>
+        <v>-26.4128016</v>
       </c>
       <c r="Q75">
-        <v>-17.9652232</v>
+        <v>-18.7128016</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2037859366412939</v>
+        <v>0.2098623188198051</v>
       </c>
       <c r="T75">
-        <v>2.893567911954542</v>
+        <v>3.004858985491255</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1430217887515209</v>
+        <v>0.1410890618765004</v>
       </c>
       <c r="W75">
-        <v>0.1720812248186946</v>
+        <v>0.1724693163751987</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5297103287093368</v>
+        <v>0.5225520810240754</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1821914970107964</v>
+        <v>0.1837414970107964</v>
       </c>
       <c r="C76">
-        <v>-189.785054343821</v>
+        <v>-196.7156721871761</v>
       </c>
       <c r="D76">
-        <v>162.914945656179</v>
+        <v>161.0843278128239</v>
       </c>
       <c r="E76">
-        <v>313.6</v>
+        <v>318.7</v>
       </c>
       <c r="F76">
-        <v>377.4</v>
+        <v>382.5</v>
       </c>
       <c r="G76">
         <v>24.7</v>
@@ -7519,37 +7519,37 @@
         <v>39.6</v>
       </c>
       <c r="M76">
-        <v>75.78192</v>
+        <v>76.806</v>
       </c>
       <c r="N76">
-        <v>-36.18192</v>
+        <v>-37.206</v>
       </c>
       <c r="O76">
-        <v>-9.7691184</v>
+        <v>-10.04562</v>
       </c>
       <c r="P76">
-        <v>-26.4128016</v>
+        <v>-27.16038</v>
       </c>
       <c r="Q76">
-        <v>-18.7128016</v>
+        <v>-19.46038</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2098623188198051</v>
+        <v>0.2164248115725974</v>
       </c>
       <c r="T76">
-        <v>3.004858985491255</v>
+        <v>3.125053344910905</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1410890618765004</v>
+        <v>0.1392078743848137</v>
       </c>
       <c r="W76">
-        <v>0.1724693163751987</v>
+        <v>0.1728470588235294</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5225520810240754</v>
+        <v>0.5155847199437544</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1837414970107964</v>
+        <v>0.1852914970107964</v>
       </c>
       <c r="C77">
-        <v>-196.7156721871761</v>
+        <v>-203.6056071542556</v>
       </c>
       <c r="D77">
-        <v>161.0843278128239</v>
+        <v>159.2943928457445</v>
       </c>
       <c r="E77">
-        <v>318.7</v>
+        <v>323.8</v>
       </c>
       <c r="F77">
-        <v>382.5</v>
+        <v>387.6</v>
       </c>
       <c r="G77">
         <v>24.7</v>
@@ -7601,37 +7601,37 @@
         <v>39.6</v>
       </c>
       <c r="M77">
-        <v>76.806</v>
+        <v>77.83008000000001</v>
       </c>
       <c r="N77">
-        <v>-37.206</v>
+        <v>-38.23008000000001</v>
       </c>
       <c r="O77">
-        <v>-10.04562</v>
+        <v>-10.3221216</v>
       </c>
       <c r="P77">
-        <v>-27.16038</v>
+        <v>-27.90795840000001</v>
       </c>
       <c r="Q77">
-        <v>-19.46038</v>
+        <v>-20.20795840000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2164248115725974</v>
+        <v>0.2235341787214556</v>
       </c>
       <c r="T77">
-        <v>3.125053344910905</v>
+        <v>3.25526390094886</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1392078743848137</v>
+        <v>0.1373761918271188</v>
       </c>
       <c r="W77">
-        <v>0.1728470588235294</v>
+        <v>0.1732148606811146</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5155847199437544</v>
+        <v>0.5088007104708102</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1852914970107964</v>
+        <v>0.1868414970107964</v>
       </c>
       <c r="C78">
-        <v>-203.6056071542556</v>
+        <v>-210.4562005196393</v>
       </c>
       <c r="D78">
-        <v>159.2943928457445</v>
+        <v>157.5437994803607</v>
       </c>
       <c r="E78">
-        <v>323.8</v>
+        <v>328.9</v>
       </c>
       <c r="F78">
-        <v>387.6</v>
+        <v>392.7</v>
       </c>
       <c r="G78">
         <v>24.7</v>
@@ -7683,37 +7683,37 @@
         <v>39.6</v>
       </c>
       <c r="M78">
-        <v>77.83008000000001</v>
+        <v>78.85415999999999</v>
       </c>
       <c r="N78">
-        <v>-38.23008000000001</v>
+        <v>-39.25415999999999</v>
       </c>
       <c r="O78">
-        <v>-10.3221216</v>
+        <v>-10.5986232</v>
       </c>
       <c r="P78">
-        <v>-27.90795840000001</v>
+        <v>-28.65553679999999</v>
       </c>
       <c r="Q78">
-        <v>-20.20795840000001</v>
+        <v>-20.9555368</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2235341787214556</v>
+        <v>0.231261751709345</v>
       </c>
       <c r="T78">
-        <v>3.25526390094886</v>
+        <v>3.396797114033593</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1373761918271188</v>
+        <v>0.1355920854397536</v>
       </c>
       <c r="W78">
-        <v>0.1732148606811146</v>
+        <v>0.1735731092436975</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5088007104708102</v>
+        <v>0.5021929090361245</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1868414970107964</v>
+        <v>0.2164296056379829</v>
       </c>
       <c r="C79">
-        <v>-210.4562005196393</v>
+        <v>-242.8751586519961</v>
       </c>
       <c r="D79">
-        <v>157.5437994803607</v>
+        <v>130.2248413480039</v>
       </c>
       <c r="E79">
-        <v>328.9</v>
+        <v>334</v>
       </c>
       <c r="F79">
-        <v>392.7</v>
+        <v>397.8</v>
       </c>
       <c r="G79">
         <v>24.7</v>
@@ -7765,45 +7765,45 @@
         <v>39.6</v>
       </c>
       <c r="M79">
-        <v>78.85415999999999</v>
+        <v>93.80124000000001</v>
       </c>
       <c r="N79">
-        <v>-39.25415999999999</v>
+        <v>-54.20124000000001</v>
       </c>
       <c r="O79">
-        <v>-10.5986232</v>
+        <v>-14.6343348</v>
       </c>
       <c r="P79">
-        <v>-28.65553679999999</v>
+        <v>-39.5669052</v>
       </c>
       <c r="Q79">
-        <v>-20.9555368</v>
+        <v>-31.86690520000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.231261751709345</v>
+        <v>0.2430468705469811</v>
       </c>
       <c r="T79">
-        <v>3.396797114033593</v>
+        <v>3.612645704307683</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1355920854397536</v>
+        <v>0.1139856999758212</v>
       </c>
       <c r="W79">
-        <v>0.1735731092436975</v>
+        <v>0.2089221719457014</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5021929090361245</v>
+        <v>0.4221692591697082</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2164296056379829</v>
+        <v>0.2183296056379829</v>
       </c>
       <c r="C80">
-        <v>-242.8751586519961</v>
+        <v>-249.4092730907689</v>
       </c>
       <c r="D80">
-        <v>130.2248413480039</v>
+        <v>128.7907269092311</v>
       </c>
       <c r="E80">
-        <v>334</v>
+        <v>339.1</v>
       </c>
       <c r="F80">
-        <v>397.8</v>
+        <v>402.9</v>
       </c>
       <c r="G80">
         <v>24.7</v>
@@ -7847,37 +7847,37 @@
         <v>39.6</v>
       </c>
       <c r="M80">
-        <v>93.80124000000001</v>
+        <v>95.00382000000002</v>
       </c>
       <c r="N80">
-        <v>-54.20124000000001</v>
+        <v>-55.40382000000002</v>
       </c>
       <c r="O80">
-        <v>-14.6343348</v>
+        <v>-14.95903140000001</v>
       </c>
       <c r="P80">
-        <v>-39.5669052</v>
+        <v>-40.44478860000001</v>
       </c>
       <c r="Q80">
-        <v>-31.86690520000001</v>
+        <v>-32.74478860000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2430468705469811</v>
+        <v>0.2524395786682659</v>
       </c>
       <c r="T80">
-        <v>3.612645704307683</v>
+        <v>3.784676452131858</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1139856999758212</v>
+        <v>0.1125428430141019</v>
       </c>
       <c r="W80">
-        <v>0.2089221719457014</v>
+        <v>0.2092623976172747</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4221692591697082</v>
+        <v>0.4168253444966739</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2183296056379829</v>
+        <v>0.2202296056379829</v>
       </c>
       <c r="C81">
-        <v>-249.4092730907689</v>
+        <v>-255.9121449268459</v>
       </c>
       <c r="D81">
-        <v>128.7907269092311</v>
+        <v>127.3878550731541</v>
       </c>
       <c r="E81">
-        <v>339.1</v>
+        <v>344.2</v>
       </c>
       <c r="F81">
-        <v>402.9</v>
+        <v>408</v>
       </c>
       <c r="G81">
         <v>24.7</v>
@@ -7929,37 +7929,37 @@
         <v>39.6</v>
       </c>
       <c r="M81">
-        <v>95.00382000000002</v>
+        <v>96.2064</v>
       </c>
       <c r="N81">
-        <v>-55.40382000000002</v>
+        <v>-56.6064</v>
       </c>
       <c r="O81">
-        <v>-14.95903140000001</v>
+        <v>-15.283728</v>
       </c>
       <c r="P81">
-        <v>-40.44478860000001</v>
+        <v>-41.322672</v>
       </c>
       <c r="Q81">
-        <v>-32.74478860000001</v>
+        <v>-33.622672</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2524395786682659</v>
+        <v>0.2627715576016792</v>
       </c>
       <c r="T81">
-        <v>3.784676452131858</v>
+        <v>3.973910274738451</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1125428430141019</v>
+        <v>0.1111360574764257</v>
       </c>
       <c r="W81">
-        <v>0.2092623976172747</v>
+        <v>0.2095941176470588</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4168253444966739</v>
+        <v>0.4116150276904655</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2202296056379829</v>
+        <v>0.2221296056379829</v>
       </c>
       <c r="C82">
-        <v>-255.9121449268459</v>
+        <v>-262.3847841031389</v>
       </c>
       <c r="D82">
-        <v>127.3878550731541</v>
+        <v>126.0152158968611</v>
       </c>
       <c r="E82">
-        <v>344.2</v>
+        <v>349.3</v>
       </c>
       <c r="F82">
-        <v>408</v>
+        <v>413.1</v>
       </c>
       <c r="G82">
         <v>24.7</v>
@@ -8011,37 +8011,37 @@
         <v>39.6</v>
       </c>
       <c r="M82">
-        <v>96.2064</v>
+        <v>97.40898000000001</v>
       </c>
       <c r="N82">
-        <v>-56.6064</v>
+        <v>-57.80898000000001</v>
       </c>
       <c r="O82">
-        <v>-15.283728</v>
+        <v>-15.6084246</v>
       </c>
       <c r="P82">
-        <v>-41.322672</v>
+        <v>-42.20055540000001</v>
       </c>
       <c r="Q82">
-        <v>-33.622672</v>
+        <v>-34.50055540000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2627715576016792</v>
+        <v>0.2741911132649255</v>
       </c>
       <c r="T82">
-        <v>3.973910274738451</v>
+        <v>4.183063447093106</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1111360574764257</v>
+        <v>0.1097640073841241</v>
       </c>
       <c r="W82">
-        <v>0.2095941176470588</v>
+        <v>0.2099176470588235</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4116150276904655</v>
+        <v>0.4065333606819412</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2221296056379829</v>
+        <v>0.2240296056379829</v>
       </c>
       <c r="C83">
-        <v>-262.3847841031389</v>
+        <v>-268.828157496953</v>
       </c>
       <c r="D83">
-        <v>126.0152158968611</v>
+        <v>124.671842503047</v>
       </c>
       <c r="E83">
-        <v>349.3</v>
+        <v>354.4</v>
       </c>
       <c r="F83">
-        <v>413.1</v>
+        <v>418.2</v>
       </c>
       <c r="G83">
         <v>24.7</v>
@@ -8093,37 +8093,37 @@
         <v>39.6</v>
       </c>
       <c r="M83">
-        <v>97.40898000000001</v>
+        <v>98.61156000000001</v>
       </c>
       <c r="N83">
-        <v>-57.80898000000001</v>
+        <v>-59.01156000000001</v>
       </c>
       <c r="O83">
-        <v>-15.6084246</v>
+        <v>-15.9331212</v>
       </c>
       <c r="P83">
-        <v>-42.20055540000001</v>
+        <v>-43.07843880000001</v>
       </c>
       <c r="Q83">
-        <v>-34.50055540000001</v>
+        <v>-35.37843880000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2741911132649255</v>
+        <v>0.2868795084463103</v>
       </c>
       <c r="T83">
-        <v>4.183063447093106</v>
+        <v>4.415455860820502</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1097640073841241</v>
+        <v>0.1084254219282202</v>
       </c>
       <c r="W83">
-        <v>0.2099176470588235</v>
+        <v>0.2102332855093257</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4065333606819412</v>
+        <v>0.4015756367711858</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2240296056379829</v>
+        <v>0.2259296056379829</v>
       </c>
       <c r="C84">
-        <v>-268.828157496953</v>
+        <v>-275.2431911912578</v>
       </c>
       <c r="D84">
-        <v>124.671842503047</v>
+        <v>123.3568088087422</v>
       </c>
       <c r="E84">
-        <v>354.4</v>
+        <v>359.5</v>
       </c>
       <c r="F84">
-        <v>418.2</v>
+        <v>423.3</v>
       </c>
       <c r="G84">
         <v>24.7</v>
@@ -8175,37 +8175,37 @@
         <v>39.6</v>
       </c>
       <c r="M84">
-        <v>98.61156000000001</v>
+        <v>99.81414000000001</v>
       </c>
       <c r="N84">
-        <v>-59.01156000000001</v>
+        <v>-60.21414000000001</v>
       </c>
       <c r="O84">
-        <v>-15.9331212</v>
+        <v>-16.2578178</v>
       </c>
       <c r="P84">
-        <v>-43.07843880000001</v>
+        <v>-43.9563222</v>
       </c>
       <c r="Q84">
-        <v>-35.37843880000001</v>
+        <v>-36.25632220000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2868795084463103</v>
+        <v>0.3010606560019756</v>
       </c>
       <c r="T84">
-        <v>4.415455860820502</v>
+        <v>4.675188558515826</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1084254219282202</v>
+        <v>0.1071190915435428</v>
       </c>
       <c r="W84">
-        <v>0.2102332855093257</v>
+        <v>0.2105413182140326</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4015756367711858</v>
+        <v>0.3967373760871956</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2259296056379829</v>
+        <v>0.2278296056379829</v>
       </c>
       <c r="C85">
-        <v>-275.2431911912578</v>
+        <v>-281.6307726037163</v>
       </c>
       <c r="D85">
-        <v>123.3568088087422</v>
+        <v>122.0692273962838</v>
       </c>
       <c r="E85">
-        <v>359.5</v>
+        <v>364.6</v>
       </c>
       <c r="F85">
-        <v>423.3</v>
+        <v>428.4</v>
       </c>
       <c r="G85">
         <v>24.7</v>
@@ -8257,37 +8257,37 @@
         <v>39.6</v>
       </c>
       <c r="M85">
-        <v>99.81414000000001</v>
+        <v>101.01672</v>
       </c>
       <c r="N85">
-        <v>-60.21414000000001</v>
+        <v>-61.41672000000001</v>
       </c>
       <c r="O85">
-        <v>-16.2578178</v>
+        <v>-16.5825144</v>
       </c>
       <c r="P85">
-        <v>-43.9563222</v>
+        <v>-44.8342056</v>
       </c>
       <c r="Q85">
-        <v>-36.25632220000001</v>
+        <v>-37.13420560000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3010606560019756</v>
+        <v>0.3170144470020991</v>
       </c>
       <c r="T85">
-        <v>4.675188558515826</v>
+        <v>4.967387843423066</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1071190915435428</v>
+        <v>0.1058438642632626</v>
       </c>
       <c r="W85">
-        <v>0.2105413182140326</v>
+        <v>0.2108420168067227</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3967373760871956</v>
+        <v>0.3920143120861576</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2278296056379829</v>
+        <v>0.2297296056379829</v>
       </c>
       <c r="C86">
-        <v>-281.6307726037162</v>
+        <v>-287.9917524837549</v>
       </c>
       <c r="D86">
-        <v>122.0692273962838</v>
+        <v>120.8082475162451</v>
       </c>
       <c r="E86">
-        <v>364.6</v>
+        <v>369.7</v>
       </c>
       <c r="F86">
-        <v>428.4</v>
+        <v>433.5</v>
       </c>
       <c r="G86">
         <v>24.7</v>
@@ -8339,37 +8339,37 @@
         <v>39.6</v>
       </c>
       <c r="M86">
-        <v>101.01672</v>
+        <v>102.2193</v>
       </c>
       <c r="N86">
-        <v>-61.41671999999999</v>
+        <v>-62.6193</v>
       </c>
       <c r="O86">
-        <v>-16.5825144</v>
+        <v>-16.907211</v>
       </c>
       <c r="P86">
-        <v>-44.83420559999999</v>
+        <v>-45.71208900000001</v>
       </c>
       <c r="Q86">
-        <v>-37.13420559999999</v>
+        <v>-38.01208900000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3170144470020989</v>
+        <v>0.3350954101355722</v>
       </c>
       <c r="T86">
-        <v>4.967387843423062</v>
+        <v>5.2985470329846</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1058438642632626</v>
+        <v>0.1045986423307536</v>
       </c>
       <c r="W86">
-        <v>0.2108420168067227</v>
+        <v>0.2111356401384083</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3920143120861577</v>
+        <v>0.3874023790027911</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2297296056379829</v>
+        <v>0.2316296056379829</v>
       </c>
       <c r="C87">
-        <v>-287.9917524837549</v>
+        <v>-294.3269467871212</v>
       </c>
       <c r="D87">
-        <v>120.8082475162451</v>
+        <v>119.5730532128787</v>
       </c>
       <c r="E87">
-        <v>369.7</v>
+        <v>374.8</v>
       </c>
       <c r="F87">
-        <v>433.5</v>
+        <v>438.6</v>
       </c>
       <c r="G87">
         <v>24.7</v>
@@ -8421,37 +8421,37 @@
         <v>39.6</v>
       </c>
       <c r="M87">
-        <v>102.2193</v>
+        <v>103.42188</v>
       </c>
       <c r="N87">
-        <v>-62.6193</v>
+        <v>-63.82188</v>
       </c>
       <c r="O87">
-        <v>-16.907211</v>
+        <v>-17.2319076</v>
       </c>
       <c r="P87">
-        <v>-45.71208900000001</v>
+        <v>-46.5899724</v>
       </c>
       <c r="Q87">
-        <v>-38.01208900000001</v>
+        <v>-38.8899724</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3350954101355722</v>
+        <v>0.3557593680023988</v>
       </c>
       <c r="T87">
-        <v>5.2985470329846</v>
+        <v>5.677014678197786</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1045986423307536</v>
+        <v>0.1033823790478379</v>
       </c>
       <c r="W87">
-        <v>0.2111356401384083</v>
+        <v>0.2114224350205198</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3874023790027911</v>
+        <v>0.3828977001771772</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2316296056379829</v>
+        <v>0.2335296056379829</v>
       </c>
       <c r="C88">
-        <v>-294.3269467871212</v>
+        <v>-300.6371384366077</v>
       </c>
       <c r="D88">
-        <v>119.5730532128787</v>
+        <v>118.3628615633923</v>
       </c>
       <c r="E88">
-        <v>374.8</v>
+        <v>379.9</v>
       </c>
       <c r="F88">
-        <v>438.6</v>
+        <v>443.7</v>
       </c>
       <c r="G88">
         <v>24.7</v>
@@ -8503,37 +8503,37 @@
         <v>39.6</v>
       </c>
       <c r="M88">
-        <v>103.42188</v>
+        <v>104.62446</v>
       </c>
       <c r="N88">
-        <v>-63.82188</v>
+        <v>-65.02446</v>
       </c>
       <c r="O88">
-        <v>-17.2319076</v>
+        <v>-17.5566042</v>
       </c>
       <c r="P88">
-        <v>-46.5899724</v>
+        <v>-47.4678558</v>
       </c>
       <c r="Q88">
-        <v>-38.8899724</v>
+        <v>-39.76785580000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3557593680023988</v>
+        <v>0.3796023963102756</v>
       </c>
       <c r="T88">
-        <v>5.677014678197786</v>
+        <v>6.113708114982231</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1033823790478379</v>
+        <v>0.1021940758403914</v>
       </c>
       <c r="W88">
-        <v>0.2114224350205198</v>
+        <v>0.2117026369168357</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3828977001771772</v>
+        <v>0.3784965771866349</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2335296056379829</v>
+        <v>0.2354296056379829</v>
       </c>
       <c r="C89">
-        <v>-300.6371384366077</v>
+        <v>-306.9230789769249</v>
       </c>
       <c r="D89">
-        <v>118.3628615633923</v>
+        <v>117.1769210230751</v>
       </c>
       <c r="E89">
-        <v>379.9</v>
+        <v>385</v>
       </c>
       <c r="F89">
-        <v>443.7</v>
+        <v>448.8</v>
       </c>
       <c r="G89">
         <v>24.7</v>
@@ -8585,37 +8585,37 @@
         <v>39.6</v>
       </c>
       <c r="M89">
-        <v>104.62446</v>
+        <v>105.82704</v>
       </c>
       <c r="N89">
-        <v>-65.02446</v>
+        <v>-66.22704000000002</v>
       </c>
       <c r="O89">
-        <v>-17.5566042</v>
+        <v>-17.88130080000001</v>
       </c>
       <c r="P89">
-        <v>-47.4678558</v>
+        <v>-48.34573920000001</v>
       </c>
       <c r="Q89">
-        <v>-39.76785580000001</v>
+        <v>-40.64573920000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3796023963102756</v>
+        <v>0.4074192626694653</v>
       </c>
       <c r="T89">
-        <v>6.113708114982231</v>
+        <v>6.62318379123075</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1021940758403914</v>
+        <v>0.1010327795240233</v>
       </c>
       <c r="W89">
-        <v>0.2117026369168357</v>
+        <v>0.2119764705882353</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3784965771866349</v>
+        <v>0.3741954797186049</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2354296056379829</v>
+        <v>0.2373296056379829</v>
       </c>
       <c r="C90">
-        <v>-306.9230789769249</v>
+        <v>-313.1854901310766</v>
       </c>
       <c r="D90">
-        <v>117.1769210230751</v>
+        <v>116.0145098689235</v>
       </c>
       <c r="E90">
-        <v>385</v>
+        <v>390.1</v>
       </c>
       <c r="F90">
-        <v>448.8</v>
+        <v>453.9</v>
       </c>
       <c r="G90">
         <v>24.7</v>
@@ -8667,37 +8667,37 @@
         <v>39.6</v>
       </c>
       <c r="M90">
-        <v>105.82704</v>
+        <v>107.02962</v>
       </c>
       <c r="N90">
-        <v>-66.22704000000002</v>
+        <v>-67.42962</v>
       </c>
       <c r="O90">
-        <v>-17.88130080000001</v>
+        <v>-18.2059974</v>
       </c>
       <c r="P90">
-        <v>-48.34573920000001</v>
+        <v>-49.2236226</v>
       </c>
       <c r="Q90">
-        <v>-40.64573920000002</v>
+        <v>-41.5236226</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4074192626694653</v>
+        <v>0.4402937410939622</v>
       </c>
       <c r="T90">
-        <v>6.62318379123075</v>
+        <v>7.225291408615365</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1010327795240233</v>
+        <v>0.09989757975409051</v>
       </c>
       <c r="W90">
-        <v>0.2119764705882353</v>
+        <v>0.2122441506939855</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3741954797186049</v>
+        <v>0.3699910361262612</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2373296056379829</v>
+        <v>0.2392296056379829</v>
       </c>
       <c r="C91">
-        <v>-313.1854901310766</v>
+        <v>-319.4250652650067</v>
       </c>
       <c r="D91">
-        <v>116.0145098689235</v>
+        <v>114.8749347349934</v>
       </c>
       <c r="E91">
-        <v>390.1</v>
+        <v>395.2</v>
       </c>
       <c r="F91">
-        <v>453.9</v>
+        <v>459</v>
       </c>
       <c r="G91">
         <v>24.7</v>
@@ -8749,37 +8749,37 @@
         <v>39.6</v>
       </c>
       <c r="M91">
-        <v>107.02962</v>
+        <v>108.2322</v>
       </c>
       <c r="N91">
-        <v>-67.42962</v>
+        <v>-68.63220000000001</v>
       </c>
       <c r="O91">
-        <v>-18.2059974</v>
+        <v>-18.530694</v>
       </c>
       <c r="P91">
-        <v>-49.2236226</v>
+        <v>-50.10150600000001</v>
       </c>
       <c r="Q91">
-        <v>-41.5236226</v>
+        <v>-42.40150600000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4402937410939622</v>
+        <v>0.4797431152033584</v>
       </c>
       <c r="T91">
-        <v>7.225291408615365</v>
+        <v>7.947820549476901</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09989757975409051</v>
+        <v>0.09878760664571172</v>
       </c>
       <c r="W91">
-        <v>0.2122441506939855</v>
+        <v>0.2125058823529412</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3699910361262612</v>
+        <v>0.365880024613747</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2392296056379829</v>
+        <v>0.2411296056379829</v>
       </c>
       <c r="C92">
-        <v>-319.4250652650067</v>
+        <v>-325.6424707667666</v>
       </c>
       <c r="D92">
-        <v>114.8749347349934</v>
+        <v>113.7575292332334</v>
       </c>
       <c r="E92">
-        <v>395.2</v>
+        <v>400.3</v>
       </c>
       <c r="F92">
-        <v>459</v>
+        <v>464.1</v>
       </c>
       <c r="G92">
         <v>24.7</v>
@@ -8831,37 +8831,37 @@
         <v>39.6</v>
       </c>
       <c r="M92">
-        <v>108.2322</v>
+        <v>109.43478</v>
       </c>
       <c r="N92">
-        <v>-68.63220000000001</v>
+        <v>-69.83477999999999</v>
       </c>
       <c r="O92">
-        <v>-18.530694</v>
+        <v>-18.8553906</v>
       </c>
       <c r="P92">
-        <v>-50.10150600000001</v>
+        <v>-50.9793894</v>
       </c>
       <c r="Q92">
-        <v>-42.40150600000001</v>
+        <v>-43.2793894</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4797431152033584</v>
+        <v>0.5279590168926205</v>
       </c>
       <c r="T92">
-        <v>7.947820549476901</v>
+        <v>8.830911721641003</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09878760664571172</v>
+        <v>0.0977020285507039</v>
       </c>
       <c r="W92">
-        <v>0.2125058823529412</v>
+        <v>0.212761861667744</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.365880024613747</v>
+        <v>0.3618593650026071</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2411296056379829</v>
+        <v>0.2430296056379829</v>
       </c>
       <c r="C93">
-        <v>-325.6424707667666</v>
+        <v>-331.8383473459647</v>
       </c>
       <c r="D93">
-        <v>113.7575292332334</v>
+        <v>112.6616526540353</v>
       </c>
       <c r="E93">
-        <v>400.3</v>
+        <v>405.4</v>
       </c>
       <c r="F93">
-        <v>464.1</v>
+        <v>469.2</v>
       </c>
       <c r="G93">
         <v>24.7</v>
@@ -8913,37 +8913,37 @@
         <v>39.6</v>
       </c>
       <c r="M93">
-        <v>109.43478</v>
+        <v>110.63736</v>
       </c>
       <c r="N93">
-        <v>-69.83477999999999</v>
+        <v>-71.03736000000001</v>
       </c>
       <c r="O93">
-        <v>-18.8553906</v>
+        <v>-19.1800872</v>
       </c>
       <c r="P93">
-        <v>-50.9793894</v>
+        <v>-51.8572728</v>
       </c>
       <c r="Q93">
-        <v>-43.2793894</v>
+        <v>-44.15727280000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5279590168926205</v>
+        <v>0.5882288940041982</v>
       </c>
       <c r="T93">
-        <v>8.830911721641003</v>
+        <v>9.934775686846132</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0977020285507039</v>
+        <v>0.09664004997950058</v>
       </c>
       <c r="W93">
-        <v>0.212761861667744</v>
+        <v>0.2130122762148338</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3618593650026071</v>
+        <v>0.3579261110351875</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2430296056379829</v>
+        <v>0.2449296056379829</v>
       </c>
       <c r="C94">
-        <v>-331.8383473459647</v>
+        <v>-338.0133112588236</v>
       </c>
       <c r="D94">
-        <v>112.6616526540353</v>
+        <v>111.5866887411764</v>
       </c>
       <c r="E94">
-        <v>405.4</v>
+        <v>410.5</v>
       </c>
       <c r="F94">
-        <v>469.2</v>
+        <v>474.3</v>
       </c>
       <c r="G94">
         <v>24.7</v>
@@ -8995,37 +8995,37 @@
         <v>39.6</v>
       </c>
       <c r="M94">
-        <v>110.63736</v>
+        <v>111.83994</v>
       </c>
       <c r="N94">
-        <v>-71.03736000000001</v>
+        <v>-72.23994000000002</v>
       </c>
       <c r="O94">
-        <v>-19.1800872</v>
+        <v>-19.50478380000001</v>
       </c>
       <c r="P94">
-        <v>-51.8572728</v>
+        <v>-52.73515620000001</v>
       </c>
       <c r="Q94">
-        <v>-44.15727280000001</v>
+        <v>-45.03515620000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5882288940041982</v>
+        <v>0.6657187360047979</v>
       </c>
       <c r="T94">
-        <v>9.934775686846132</v>
+        <v>11.35402935639558</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09664004997950058</v>
+        <v>0.09560090965714037</v>
       </c>
       <c r="W94">
-        <v>0.2130122762148338</v>
+        <v>0.2132573055028463</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3579261110351875</v>
+        <v>0.3540774431745939</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2449296056379829</v>
+        <v>0.2468296056379829</v>
       </c>
       <c r="C95">
-        <v>-338.0133112588236</v>
+        <v>-344.1679554637675</v>
       </c>
       <c r="D95">
-        <v>111.5866887411764</v>
+        <v>110.5320445362326</v>
       </c>
       <c r="E95">
-        <v>410.5</v>
+        <v>415.6</v>
       </c>
       <c r="F95">
-        <v>474.3</v>
+        <v>479.4</v>
       </c>
       <c r="G95">
         <v>24.7</v>
@@ -9077,37 +9077,37 @@
         <v>39.6</v>
       </c>
       <c r="M95">
-        <v>111.83994</v>
+        <v>113.04252</v>
       </c>
       <c r="N95">
-        <v>-72.23994000000002</v>
+        <v>-73.44252</v>
       </c>
       <c r="O95">
-        <v>-19.50478380000001</v>
+        <v>-19.8294804</v>
       </c>
       <c r="P95">
-        <v>-52.73515620000001</v>
+        <v>-53.6130396</v>
       </c>
       <c r="Q95">
-        <v>-45.03515620000002</v>
+        <v>-45.9130396</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6657187360047979</v>
+        <v>0.769038525338931</v>
       </c>
       <c r="T95">
-        <v>11.35402935639558</v>
+        <v>13.24636758246151</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09560090965714037</v>
+        <v>0.09458387870334101</v>
       </c>
       <c r="W95">
-        <v>0.2132573055028463</v>
+        <v>0.2134971214017522</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3540774431745939</v>
+        <v>0.350310661864226</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2468296056379829</v>
+        <v>0.2487296056379829</v>
       </c>
       <c r="C96">
-        <v>-344.1679554637675</v>
+        <v>-350.3028507120907</v>
       </c>
       <c r="D96">
-        <v>110.5320445362326</v>
+        <v>109.4971492879094</v>
       </c>
       <c r="E96">
-        <v>415.6</v>
+        <v>420.7</v>
       </c>
       <c r="F96">
-        <v>479.4</v>
+        <v>484.5000000000001</v>
       </c>
       <c r="G96">
         <v>24.7</v>
@@ -9159,37 +9159,37 @@
         <v>39.6</v>
       </c>
       <c r="M96">
-        <v>113.04252</v>
+        <v>114.2451</v>
       </c>
       <c r="N96">
-        <v>-73.44252</v>
+        <v>-74.64510000000001</v>
       </c>
       <c r="O96">
-        <v>-19.8294804</v>
+        <v>-20.154177</v>
       </c>
       <c r="P96">
-        <v>-53.6130396</v>
+        <v>-54.49092300000001</v>
       </c>
       <c r="Q96">
-        <v>-45.9130396</v>
+        <v>-46.79092300000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.769038525338931</v>
+        <v>0.9136862304067178</v>
       </c>
       <c r="T96">
-        <v>13.24636758246151</v>
+        <v>15.89564109895382</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09458387870334101</v>
+        <v>0.09358825892751636</v>
       </c>
       <c r="W96">
-        <v>0.2134971214017522</v>
+        <v>0.2137318885448917</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.350310661864226</v>
+        <v>0.3466231812130236</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2487296056379829</v>
+        <v>0.2506296056379829</v>
       </c>
       <c r="C97">
-        <v>-350.3028507120907</v>
+        <v>-356.4185465779252</v>
       </c>
       <c r="D97">
-        <v>109.4971492879094</v>
+        <v>108.4814534220748</v>
       </c>
       <c r="E97">
-        <v>420.7</v>
+        <v>425.8</v>
       </c>
       <c r="F97">
-        <v>484.5000000000001</v>
+        <v>489.6</v>
       </c>
       <c r="G97">
         <v>24.7</v>
@@ -9241,37 +9241,37 @@
         <v>39.6</v>
       </c>
       <c r="M97">
-        <v>114.2451</v>
+        <v>115.44768</v>
       </c>
       <c r="N97">
-        <v>-74.64510000000001</v>
+        <v>-75.84768</v>
       </c>
       <c r="O97">
-        <v>-20.154177</v>
+        <v>-20.4788736</v>
       </c>
       <c r="P97">
-        <v>-54.49092300000001</v>
+        <v>-55.3688064</v>
       </c>
       <c r="Q97">
-        <v>-46.79092300000001</v>
+        <v>-47.6688064</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9136862304067178</v>
+        <v>1.130657788008398</v>
       </c>
       <c r="T97">
-        <v>15.89564109895382</v>
+        <v>19.86955137369229</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09358825892751636</v>
+        <v>0.09261338123035474</v>
       </c>
       <c r="W97">
-        <v>0.2137318885448917</v>
+        <v>0.2139617647058824</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3466231812130236</v>
+        <v>0.343012523075388</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2506296056379829</v>
+        <v>0.2525296056379829</v>
       </c>
       <c r="C98">
-        <v>-356.4185465779252</v>
+        <v>-362.5155724314108</v>
       </c>
       <c r="D98">
-        <v>108.4814534220748</v>
+        <v>107.4844275685892</v>
       </c>
       <c r="E98">
-        <v>425.8</v>
+        <v>430.9</v>
       </c>
       <c r="F98">
-        <v>489.6</v>
+        <v>494.7</v>
       </c>
       <c r="G98">
         <v>24.7</v>
@@ -9323,37 +9323,37 @@
         <v>39.6</v>
       </c>
       <c r="M98">
-        <v>115.44768</v>
+        <v>116.65026</v>
       </c>
       <c r="N98">
-        <v>-75.84768</v>
+        <v>-77.05026000000001</v>
       </c>
       <c r="O98">
-        <v>-20.4788736</v>
+        <v>-20.8035702</v>
       </c>
       <c r="P98">
-        <v>-55.3688064</v>
+        <v>-56.24668980000001</v>
       </c>
       <c r="Q98">
-        <v>-47.6688064</v>
+        <v>-48.54668980000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.130657788008395</v>
+        <v>1.49227705067786</v>
       </c>
       <c r="T98">
-        <v>19.86955137369223</v>
+        <v>26.49273516492298</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09261338123035474</v>
+        <v>0.09165860410426861</v>
       </c>
       <c r="W98">
-        <v>0.2139617647058824</v>
+        <v>0.2141869011522135</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3430125230753879</v>
+        <v>0.3394763114972911</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2525296056379829</v>
+        <v>0.2544296056379829</v>
       </c>
       <c r="C99">
-        <v>-362.5155724314108</v>
+        <v>-368.5944383586881</v>
       </c>
       <c r="D99">
-        <v>107.4844275685892</v>
+        <v>106.5055616413119</v>
       </c>
       <c r="E99">
-        <v>430.9</v>
+        <v>436</v>
       </c>
       <c r="F99">
-        <v>494.7</v>
+        <v>499.8</v>
       </c>
       <c r="G99">
         <v>24.7</v>
@@ -9405,37 +9405,37 @@
         <v>39.6</v>
       </c>
       <c r="M99">
-        <v>116.65026</v>
+        <v>117.85284</v>
       </c>
       <c r="N99">
-        <v>-77.05026000000001</v>
+        <v>-78.25283999999999</v>
       </c>
       <c r="O99">
-        <v>-20.8035702</v>
+        <v>-21.1282668</v>
       </c>
       <c r="P99">
-        <v>-56.24668980000001</v>
+        <v>-57.12457319999999</v>
       </c>
       <c r="Q99">
-        <v>-48.54668980000001</v>
+        <v>-49.4245732</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.49227705067786</v>
+        <v>2.215515576016789</v>
       </c>
       <c r="T99">
-        <v>26.49273516492298</v>
+        <v>39.73910274738446</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09165860410426861</v>
+        <v>0.09072331222565362</v>
       </c>
       <c r="W99">
-        <v>0.2141869011522135</v>
+        <v>0.2144074429771909</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3394763114972911</v>
+        <v>0.3360122675024209</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2544296056379829</v>
+        <v>0.2563296056379829</v>
       </c>
       <c r="C100">
-        <v>-368.5944383586881</v>
+        <v>-374.6556360320759</v>
       </c>
       <c r="D100">
-        <v>106.5055616413119</v>
+        <v>105.5443639679241</v>
       </c>
       <c r="E100">
-        <v>436</v>
+        <v>441.1</v>
       </c>
       <c r="F100">
-        <v>499.8</v>
+        <v>504.9</v>
       </c>
       <c r="G100">
         <v>24.7</v>
@@ -9487,37 +9487,37 @@
         <v>39.6</v>
       </c>
       <c r="M100">
-        <v>117.85284</v>
+        <v>119.05542</v>
       </c>
       <c r="N100">
-        <v>-78.25283999999999</v>
+        <v>-79.45542</v>
       </c>
       <c r="O100">
-        <v>-21.1282668</v>
+        <v>-21.4529634</v>
       </c>
       <c r="P100">
-        <v>-57.12457319999999</v>
+        <v>-58.0024566</v>
       </c>
       <c r="Q100">
-        <v>-49.4245732</v>
+        <v>-50.30245660000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.215515576016789</v>
+        <v>4.38523115203358</v>
       </c>
       <c r="T100">
-        <v>39.73910274738446</v>
+        <v>79.47820549476894</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09072331222565362</v>
+        <v>0.08980691513246522</v>
       </c>
       <c r="W100">
-        <v>0.2144074429771909</v>
+        <v>0.2146235294117647</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3360122675024209</v>
+        <v>0.3326182041943155</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2563296056379829</v>
-      </c>
-      <c r="C101">
-        <v>-374.6556360320759</v>
-      </c>
-      <c r="D101">
-        <v>105.5443639679241</v>
-      </c>
-      <c r="E101">
-        <v>441.1</v>
-      </c>
-      <c r="F101">
-        <v>504.9</v>
-      </c>
-      <c r="G101">
-        <v>24.7</v>
-      </c>
-      <c r="H101">
-        <v>446.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>47.3</v>
-      </c>
-      <c r="K101">
-        <v>7.699999999999996</v>
-      </c>
-      <c r="L101">
-        <v>39.6</v>
-      </c>
-      <c r="M101">
-        <v>119.05542</v>
-      </c>
-      <c r="N101">
-        <v>-79.45542</v>
-      </c>
-      <c r="O101">
-        <v>-21.4529634</v>
-      </c>
-      <c r="P101">
-        <v>-58.0024566</v>
-      </c>
-      <c r="Q101">
-        <v>-50.30245660000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.38523115203358</v>
-      </c>
-      <c r="T101">
-        <v>79.47820549476894</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08980691513246522</v>
-      </c>
-      <c r="W101">
-        <v>0.2146235294117647</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3326182041943155</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
